--- a/data/merged/2026-10-08/MERGED_JP_Spot-Cleaner_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_JP_Spot-Cleaner_2026-10-08.xlsx
@@ -5778,13 +5778,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5998,13 +5998,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6086,13 +6086,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6130,13 +6130,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6174,13 +6174,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6218,14 +6218,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6330,138 +6330,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId41" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="Product 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId42" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="Product 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId43" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Product 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId44" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6803,7 +6671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -12292,40 +12160,40 @@
       <c r="B24" s="11"/>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>B0H7B99X6W</t>
+          <t>B0FWCRWS4J</t>
         </is>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>PLUS MINUS ZERO</t>
+          <t>YINOLIFE</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%97%E3%83%A9%E3%82%B9%E3%83%9E%E3%82%A4%E3%83%8A%E3%82%B9%E3%82%BC%E3%83%AD/page/F8BCEE33-4642-4879-8043-6C340A3D69AB?lp_asin=B0H7B99X6W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/YINOLIFE/page/B4E9A7F4-5909-4351-B434-6EF367427B37?lp_asin=B0FWCRWS4J&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>【Amazon限定セット】±0 スチームクリーナー キッチンまわり徹底掃除セット スポンジブラシ10枚＋スポットブラシ5個＋金属ブラシ3個付き (ブラウングレー)</t>
+          <t>[业界TOP吸力20000Pa &amp; 背面收纳设计]YINOLIFE 蒸汽清洁器 1台4用 加热式 地毯清洁剂 自动浇水s100℃ 高温蒸汽,配有 5 种刷子,自动软管清洁,去除顽固污渍,去除螨虫和霉菌,彻底的沙发,汽车座椅,地毯,床垫垫,去除毛绒</t>
         </is>
       </c>
       <c r="I24" s="12"/>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H7B99X6W?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FWCRWS4J?psc=1</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51C5hYWM0yL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41aG6lp2gKL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
-          <t>B0H7B99X6W</t>
+          <t>B0FWCRWS4J</t>
         </is>
       </c>
       <c r="M24" s="12" t="inlineStr">
@@ -12339,13 +12207,13 @@
         </is>
       </c>
       <c r="O24" s="13">
-        <v>58402</v>
+        <v>59686</v>
       </c>
       <c r="P24" s="13">
-        <v>-2671</v>
+        <v>-126</v>
       </c>
       <c r="Q24" s="14">
-        <v>-0.07</v>
+        <v>0</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -12354,17 +12222,17 @@
       </c>
       <c r="S24" s="16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="T24" s="13">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U24" s="14">
-        <v>43</v>
+        <v>-0.28</v>
       </c>
       <c r="V24" s="13">
-        <v>1020800</v>
+        <v>1002400</v>
       </c>
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
@@ -12372,37 +12240,37 @@
         <v>2</v>
       </c>
       <c r="Z24" s="13">
-        <v>17600</v>
+        <v>17900</v>
       </c>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="17">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="AE24" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF24" s="18">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AG24" s="19">
-        <v>0.069</v>
+        <v>0.08929999999999999</v>
       </c>
       <c r="AH24" s="13">
-        <v>472</v>
+        <v>781</v>
       </c>
       <c r="AI24" s="14">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="AJ24"/>
       <c r="AK24" s="11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AL24" s="17">
-        <v>85</v>
+        <v>356</v>
       </c>
       <c r="AM24" s="11" t="inlineStr">
         <is>
@@ -12412,13 +12280,15 @@
       <c r="AN24" s="11"/>
       <c r="AO24" s="11"/>
       <c r="AP24"/>
-      <c r="AQ24" s="17"/>
+      <c r="AQ24" s="17">
+        <v>9</v>
+      </c>
       <c r="AR24" s="17">
         <v>1</v>
       </c>
       <c r="AS24" s="12" t="inlineStr">
         <is>
-          <t>プラスマイナスゼロ</t>
+          <t>YINOLIFE（イノライフ）公式ストア</t>
         </is>
       </c>
       <c r="AT24" s="11" t="inlineStr">
@@ -12428,17 +12298,17 @@
       </c>
       <c r="AU24" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV24" s="12" t="inlineStr">
         <is>
-          <t>中央区 東京都 1040031 JP</t>
+          <t>shenzhen guangdong 518066 CN</t>
         </is>
       </c>
       <c r="AW24" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SVARFDL9L32I</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3BEVRYR6RB3FY</t>
         </is>
       </c>
       <c r="AX24" s="11"/>
@@ -12455,7 +12325,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD24" s="11"/>
+      <c r="BD24" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE24" s="11"/>
       <c r="BF24" s="11"/>
       <c r="BG24" s="11"/>
@@ -12467,43 +12341,47 @@
       </c>
       <c r="BJ24" s="20" t="inlineStr">
         <is>
-          <t>1 Kilograms</t>
+          <t>5.35 Kilograms</t>
         </is>
       </c>
       <c r="BK24" s="20" t="inlineStr">
         <is>
-          <t>1,000.00 g</t>
+          <t>5.35 kg</t>
         </is>
       </c>
       <c r="BL24" s="20" t="inlineStr">
         <is>
-          <t>17.7奥行き x 7.5幅 x 26.7高さ cm</t>
-        </is>
-      </c>
-      <c r="BM24" s="20"/>
+          <t>44 x 35.7 x 19.9 cm</t>
+        </is>
+      </c>
+      <c r="BM24" s="20" t="inlineStr">
+        <is>
+          <t>44.00 x 35.70 x 19.90 cm</t>
+        </is>
+      </c>
       <c r="BN24" s="20" t="inlineStr">
         <is>
-          <t>1.89 kg</t>
+          <t>5.35 kg</t>
         </is>
       </c>
       <c r="BO24" s="20" t="inlineStr">
         <is>
-          <t>1.89 kg</t>
+          <t>5.35 kg</t>
         </is>
       </c>
       <c r="BP24" s="20" t="inlineStr">
         <is>
-          <t>36 x 24.5 x 17.9 cm</t>
+          <t>44.2 x 35.5 x 20.5 cm</t>
         </is>
       </c>
       <c r="BQ24" s="20" t="inlineStr">
         <is>
-          <t>36.00 x 24.50 x 17.90 cm</t>
+          <t>44.20 x 35.50 x 20.50 cm</t>
         </is>
       </c>
       <c r="BR24" s="11" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>大件</t>
         </is>
       </c>
     </row>
@@ -12514,40 +12392,40 @@
       <c r="B25" s="11"/>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>B0FWCRWS4J</t>
+          <t>B0H1LV9Z1W</t>
         </is>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>YINOLIFE</t>
+          <t>udodik</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/YINOLIFE/page/B4E9A7F4-5909-4351-B434-6EF367427B37?lp_asin=B0FWCRWS4J&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/udodik/b/ref=bl_dp_s_web_21106953051?ie=UTF8&amp;node=21106953051&amp;field-lbr_brands_browse-bin=udodik</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>[业界TOP吸力20000Pa &amp; 背面收纳设计]YINOLIFE 蒸汽清洁器 1台4用 加热式 地毯清洁剂 自动浇水s100℃ 高温蒸汽,配有 5 种刷子,自动软管清洁,去除顽固污渍,去除螨虫和霉菌,彻底的沙发,汽车座椅,地毯,床垫垫,去除毛绒</t>
+          <t>Udodik スチームクリーナ, 20種類の異なるアタッチメント付きs多機能スチームクリーナー| 温度は120°Cに達します| キッチンの油汚れ、床、ソファ、カーペット| 窓などの掃除に使用できます。</t>
         </is>
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FWCRWS4J?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H1LV9Z1W?psc=1</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41aG6lp2gKL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41hNJ+tmXEL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>B0FWCRWS4J</t>
+          <t>B0H1LV9Z1W</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
@@ -12561,13 +12439,13 @@
         </is>
       </c>
       <c r="O25" s="13">
-        <v>59686</v>
+        <v>41624</v>
       </c>
       <c r="P25" s="13">
-        <v>-126</v>
+        <v>-54614</v>
       </c>
       <c r="Q25" s="14">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -12576,55 +12454,61 @@
       </c>
       <c r="S25" s="16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T25" s="13">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="U25" s="14">
-        <v>-0.28</v>
+        <v>0.73</v>
       </c>
       <c r="V25" s="13">
-        <v>1002400</v>
-      </c>
-      <c r="W25" s="13"/>
-      <c r="X25" s="13"/>
+        <v>978752</v>
+      </c>
+      <c r="W25" s="13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X25" s="13">
+        <v>702443</v>
+      </c>
       <c r="Y25" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z25" s="13">
-        <v>17900</v>
+        <v>15293</v>
       </c>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="17">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="AE25" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF25" s="18">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AG25" s="19">
-        <v>0.08929999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AH25" s="13">
         <v>781</v>
       </c>
       <c r="AI25" s="14">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="AJ25"/>
       <c r="AK25" s="11" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AL25" s="17">
-        <v>356</v>
+        <v>127</v>
       </c>
       <c r="AM25" s="11" t="inlineStr">
         <is>
@@ -12638,11 +12522,11 @@
         <v>9</v>
       </c>
       <c r="AR25" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS25" s="12" t="inlineStr">
         <is>
-          <t>YINOLIFE（イノライフ）公式ストア</t>
+          <t>jinanrenxianchengxinxikejiyouxiangongsi</t>
         </is>
       </c>
       <c r="AT25" s="11" t="inlineStr">
@@ -12657,20 +12541,16 @@
       </c>
       <c r="AV25" s="12" t="inlineStr">
         <is>
-          <t>shenzhen guangdong 518066 CN</t>
+          <t>济南市 山东 250100 CN</t>
         </is>
       </c>
       <c r="AW25" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3BEVRYR6RB3FY</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3LLGXOKFXGBZY</t>
         </is>
       </c>
       <c r="AX25" s="11"/>
-      <c r="AY25" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY25" s="11"/>
       <c r="AZ25" s="11"/>
       <c r="BA25" s="11"/>
       <c r="BB25" s="11"/>
@@ -12679,58 +12559,42 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD25" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD25" s="11"/>
       <c r="BE25" s="11"/>
       <c r="BF25" s="11"/>
       <c r="BG25" s="11"/>
       <c r="BH25" s="12"/>
-      <c r="BI25" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
+      <c r="BI25" s="20"/>
       <c r="BJ25" s="20" t="inlineStr">
         <is>
-          <t>5.35 Kilograms</t>
+          <t>5.39 Kilograms</t>
         </is>
       </c>
       <c r="BK25" s="20" t="inlineStr">
         <is>
-          <t>5.35 kg</t>
-        </is>
-      </c>
-      <c r="BL25" s="20" t="inlineStr">
-        <is>
-          <t>44 x 35.7 x 19.9 cm</t>
-        </is>
-      </c>
-      <c r="BM25" s="20" t="inlineStr">
-        <is>
-          <t>44.00 x 35.70 x 19.90 cm</t>
-        </is>
-      </c>
+          <t>5.39 kg</t>
+        </is>
+      </c>
+      <c r="BL25" s="20"/>
+      <c r="BM25" s="20"/>
       <c r="BN25" s="20" t="inlineStr">
         <is>
-          <t>5.35 kg</t>
+          <t>5.39 kg</t>
         </is>
       </c>
       <c r="BO25" s="20" t="inlineStr">
         <is>
-          <t>5.35 kg</t>
+          <t>5.39 kg</t>
         </is>
       </c>
       <c r="BP25" s="20" t="inlineStr">
         <is>
-          <t>44.2 x 35.5 x 20.5 cm</t>
+          <t>46 x 29 x 28 cm</t>
         </is>
       </c>
       <c r="BQ25" s="20" t="inlineStr">
         <is>
-          <t>44.20 x 35.50 x 20.50 cm</t>
+          <t>46.00 x 29.00 x 28.00 cm</t>
         </is>
       </c>
       <c r="BR25" s="11" t="inlineStr">
@@ -12746,40 +12610,40 @@
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>B0H1LV9Z1W</t>
+          <t>B0BLHZDTDP</t>
         </is>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="12"/>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>udodik</t>
+          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/udodik/b/ref=bl_dp_s_web_21106953051?ie=UTF8&amp;node=21106953051&amp;field-lbr_brands_browse-bin=udodik</t>
+          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0BLHZDTDP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>Udodik スチームクリーナ, 20種類の異なるアタッチメント付きs多機能スチームクリーナー| 温度は120°Cに達します| キッチンの油汚れ、床、ソファ、カーペット| 窓などの掃除に使用できます。</t>
+          <t>IRIS OHYAMA(IRIS OHYAMA) 在没有电源的地方也可使用 无绳式充电器 更换电池式 车内也可轻松清洗 降低驾驶声音 安静 小孩子 宠物 易于清洗的回收水箱 可用热水清洗 轻便 小巧 推荐法人使用 RNS-B400D</t>
         </is>
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H1LV9Z1W?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0BLHZDTDP?psc=1</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41hNJ+tmXEL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41B2GvpD-eL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>B0H1LV9Z1W</t>
+          <t>B0BLHZDTDP</t>
         </is>
       </c>
       <c r="M26" s="12" t="inlineStr">
@@ -12793,13 +12657,13 @@
         </is>
       </c>
       <c r="O26" s="13">
-        <v>41624</v>
+        <v>48574</v>
       </c>
       <c r="P26" s="13">
-        <v>-54614</v>
+        <v>-17096</v>
       </c>
       <c r="Q26" s="14">
-        <v>-1.05</v>
+        <v>-0.54</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -12808,17 +12672,17 @@
       </c>
       <c r="S26" s="16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T26" s="13">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="U26" s="14">
-        <v>0.73</v>
+        <v>0.27</v>
       </c>
       <c r="V26" s="13">
-        <v>978752</v>
+        <v>963800</v>
       </c>
       <c r="W26" s="13" t="inlineStr">
         <is>
@@ -12826,31 +12690,31 @@
         </is>
       </c>
       <c r="X26" s="13">
-        <v>702443</v>
+        <v>649366</v>
       </c>
       <c r="Y26" s="17">
         <v>1</v>
       </c>
       <c r="Z26" s="13">
-        <v>15293</v>
+        <v>12200</v>
       </c>
       <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="17">
-        <v>30</v>
+        <v>129</v>
       </c>
       <c r="AE26" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF26" s="18">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG26" s="19">
-        <v>0.0625</v>
+        <v>0.038</v>
       </c>
       <c r="AH26" s="13">
-        <v>781</v>
+        <v>675</v>
       </c>
       <c r="AI26" s="14">
         <v>0.8</v>
@@ -12858,11 +12722,11 @@
       <c r="AJ26"/>
       <c r="AK26" s="11" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AL26" s="17">
-        <v>127</v>
+        <v>1433</v>
       </c>
       <c r="AM26" s="11" t="inlineStr">
         <is>
@@ -12876,11 +12740,11 @@
         <v>9</v>
       </c>
       <c r="AR26" s="17">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="AS26" s="12" t="inlineStr">
         <is>
-          <t>jinanrenxianchengxinxikejiyouxiangongsi</t>
+          <t>佐々木倉庫</t>
         </is>
       </c>
       <c r="AT26" s="11" t="inlineStr">
@@ -12890,17 +12754,17 @@
       </c>
       <c r="AU26" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV26" s="12" t="inlineStr">
         <is>
-          <t>济南市 山东 250100 CN</t>
+          <t>鯖江市 福井県 9160019 JP</t>
         </is>
       </c>
       <c r="AW26" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3LLGXOKFXGBZY</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A16H9JXI44PW5O</t>
         </is>
       </c>
       <c r="AX26" s="11"/>
@@ -12913,7 +12777,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD26" s="11"/>
+      <c r="BD26" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE26" s="11"/>
       <c r="BF26" s="11"/>
       <c r="BG26" s="11"/>
@@ -12921,34 +12789,42 @@
       <c r="BI26" s="20"/>
       <c r="BJ26" s="20" t="inlineStr">
         <is>
-          <t>5.39 Kilograms</t>
+          <t>2.4 Kilograms</t>
         </is>
       </c>
       <c r="BK26" s="20" t="inlineStr">
         <is>
-          <t>5.39 kg</t>
-        </is>
-      </c>
-      <c r="BL26" s="20"/>
-      <c r="BM26" s="20"/>
+          <t>2.40 kg</t>
+        </is>
+      </c>
+      <c r="BL26" s="20" t="inlineStr">
+        <is>
+          <t>21.3 x 23.3 x 27.7 cm</t>
+        </is>
+      </c>
+      <c r="BM26" s="20" t="inlineStr">
+        <is>
+          <t>21.30 x 23.30 x 27.70 cm</t>
+        </is>
+      </c>
       <c r="BN26" s="20" t="inlineStr">
         <is>
-          <t>5.39 kg</t>
+          <t>3.45 kg</t>
         </is>
       </c>
       <c r="BO26" s="20" t="inlineStr">
         <is>
-          <t>5.39 kg</t>
+          <t>3.45 kg</t>
         </is>
       </c>
       <c r="BP26" s="20" t="inlineStr">
         <is>
-          <t>46 x 29 x 28 cm</t>
+          <t>38.8 x 27.7 x 27.3 cm</t>
         </is>
       </c>
       <c r="BQ26" s="20" t="inlineStr">
         <is>
-          <t>46.00 x 29.00 x 28.00 cm</t>
+          <t>38.80 x 27.70 x 27.30 cm</t>
         </is>
       </c>
       <c r="BR26" s="11" t="inlineStr">
@@ -12964,40 +12840,40 @@
       <c r="B27" s="11"/>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>B0BLHZDTDP</t>
+          <t>B0GHMZNCVL</t>
         </is>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
+          <t>Karcher</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0BLHZDTDP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Karcher</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>IRIS OHYAMA(IRIS OHYAMA) 在没有电源的地方也可使用 无绳式充电器 更换电池式 车内也可轻松清洗 降低驾驶声音 安静 小孩子 宠物 易于清洗的回收水箱 可用热水清洗 轻便 小巧 推荐法人使用 RNS-B400D</t>
+          <t>Takaga Karcher 家用蒸汽清洁机(SC JTK20)</t>
         </is>
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0BLHZDTDP?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GHMZNCVL?psc=1</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41B2GvpD-eL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41eNQ9I14nL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>B0BLHZDTDP</t>
+          <t>B0GHMZNCVL</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
@@ -13011,13 +12887,13 @@
         </is>
       </c>
       <c r="O27" s="13">
-        <v>48574</v>
+        <v>43512</v>
       </c>
       <c r="P27" s="13">
-        <v>-17096</v>
+        <v>-16780</v>
       </c>
       <c r="Q27" s="14">
-        <v>-0.54</v>
+        <v>-0.47</v>
       </c>
       <c r="R27" s="15" t="inlineStr">
         <is>
@@ -13026,49 +12902,43 @@
       </c>
       <c r="S27" s="16" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T27" s="13">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="U27" s="14">
-        <v>0.27</v>
+        <v>0.07</v>
       </c>
       <c r="V27" s="13">
-        <v>963800</v>
-      </c>
-      <c r="W27" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X27" s="13">
-        <v>649366</v>
-      </c>
+        <v>869250</v>
+      </c>
+      <c r="W27" s="13"/>
+      <c r="X27" s="13"/>
       <c r="Y27" s="17">
         <v>1</v>
       </c>
       <c r="Z27" s="13">
-        <v>12200</v>
+        <v>14250</v>
       </c>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="17">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="AE27" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF27" s="18">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AG27" s="19">
-        <v>0.038</v>
+        <v>0.032799999999999996</v>
       </c>
       <c r="AH27" s="13">
-        <v>675</v>
+        <v>781</v>
       </c>
       <c r="AI27" s="14">
         <v>0.8</v>
@@ -13076,11 +12946,11 @@
       <c r="AJ27"/>
       <c r="AK27" s="11" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AL27" s="17">
-        <v>1433</v>
+        <v>261</v>
       </c>
       <c r="AM27" s="11" t="inlineStr">
         <is>
@@ -13091,14 +12961,14 @@
       <c r="AO27" s="11"/>
       <c r="AP27"/>
       <c r="AQ27" s="17">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AR27" s="17">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AS27" s="12" t="inlineStr">
         <is>
-          <t>佐々木倉庫</t>
+          <t>Tetoria岸和田</t>
         </is>
       </c>
       <c r="AT27" s="11" t="inlineStr">
@@ -13113,12 +12983,12 @@
       </c>
       <c r="AV27" s="12" t="inlineStr">
         <is>
-          <t>鯖江市 福井県 9160019 JP</t>
+          <t>岸和田市 大阪府 5960006 JP</t>
         </is>
       </c>
       <c r="AW27" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A16H9JXI44PW5O</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZHWG2831WCH8</t>
         </is>
       </c>
       <c r="AX27" s="11"/>
@@ -13126,16 +12996,8 @@
       <c r="AZ27" s="11"/>
       <c r="BA27" s="11"/>
       <c r="BB27" s="11"/>
-      <c r="BC27" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD27" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC27" s="11"/>
+      <c r="BD27" s="11"/>
       <c r="BE27" s="11"/>
       <c r="BF27" s="11"/>
       <c r="BG27" s="11"/>
@@ -13143,42 +13005,42 @@
       <c r="BI27" s="20"/>
       <c r="BJ27" s="20" t="inlineStr">
         <is>
-          <t>2.4 Kilograms</t>
+          <t>4.54 Kilograms</t>
         </is>
       </c>
       <c r="BK27" s="20" t="inlineStr">
         <is>
-          <t>2.40 kg</t>
+          <t>4.54 kg</t>
         </is>
       </c>
       <c r="BL27" s="20" t="inlineStr">
         <is>
-          <t>21.3 x 23.3 x 27.7 cm</t>
+          <t>47.3 x 31.9 x 25 cm</t>
         </is>
       </c>
       <c r="BM27" s="20" t="inlineStr">
         <is>
-          <t>21.30 x 23.30 x 27.70 cm</t>
+          <t>47.30 x 31.90 x 25.00 cm</t>
         </is>
       </c>
       <c r="BN27" s="20" t="inlineStr">
         <is>
-          <t>3.45 kg</t>
+          <t>4.54 kg</t>
         </is>
       </c>
       <c r="BO27" s="20" t="inlineStr">
         <is>
-          <t>3.45 kg</t>
+          <t>4.54 kg</t>
         </is>
       </c>
       <c r="BP27" s="20" t="inlineStr">
         <is>
-          <t>38.8 x 27.7 x 27.3 cm</t>
+          <t>47.3 x 31.9 x 25 cm</t>
         </is>
       </c>
       <c r="BQ27" s="20" t="inlineStr">
         <is>
-          <t>38.80 x 27.70 x 27.30 cm</t>
+          <t>47.30 x 31.90 x 25.00 cm</t>
         </is>
       </c>
       <c r="BR27" s="11" t="inlineStr">
@@ -13194,40 +13056,40 @@
       <c r="B28" s="11"/>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>B0GHMZNCVL</t>
+          <t>B07GXPG63H</t>
         </is>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="12"/>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Karcher</t>
+          <t>KÄRCHER</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Karcher</t>
+          <t>https://www.amazon.co.jp/stores/%E3%82%B1%E3%83%AB%E3%83%92%E3%83%A3%E3%83%BCKARCHER/page/C3335239-5EF7-43A7-B432-CEBBBE4E3C9B?lp_asin=B07GXPG63H&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>Takaga Karcher 家用蒸汽清洁机(SC JTK20)</t>
+          <t>Karcher 蒸汽清洁器 SC2 EasyFix 1.512-059.0 清扫/除菌</t>
         </is>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GHMZNCVL?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B07GXPG63H?psc=1</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41eNQ9I14nL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41H+7reLbSL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
-          <t>B0GHMZNCVL</t>
+          <t>B07GXPG63H</t>
         </is>
       </c>
       <c r="M28" s="12" t="inlineStr">
@@ -13241,13 +13103,13 @@
         </is>
       </c>
       <c r="O28" s="13">
-        <v>43512</v>
+        <v>49731</v>
       </c>
       <c r="P28" s="13">
-        <v>-16780</v>
+        <v>35424</v>
       </c>
       <c r="Q28" s="14">
-        <v>-0.47</v>
+        <v>0.4</v>
       </c>
       <c r="R28" s="15" t="inlineStr">
         <is>
@@ -13256,17 +13118,17 @@
       </c>
       <c r="S28" s="16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="T28" s="13">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="U28" s="14">
-        <v>0.07</v>
+        <v>0.64</v>
       </c>
       <c r="V28" s="13">
-        <v>869250</v>
+        <v>846720</v>
       </c>
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
@@ -13274,60 +13136,62 @@
         <v>1</v>
       </c>
       <c r="Z28" s="13">
-        <v>14250</v>
+        <v>18816</v>
       </c>
       <c r="AA28"/>
       <c r="AB28"/>
-      <c r="AC28" s="2"/>
+      <c r="AC28" s="2">
+        <v>18</v>
+      </c>
       <c r="AD28" s="17">
-        <v>9</v>
+        <v>606</v>
       </c>
       <c r="AE28" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF28" s="18">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AG28" s="19">
-        <v>0.032799999999999996</v>
+        <v>0</v>
       </c>
       <c r="AH28" s="13">
         <v>781</v>
       </c>
       <c r="AI28" s="14">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="AJ28"/>
       <c r="AK28" s="11" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AL28" s="17">
-        <v>261</v>
+        <v>2940</v>
       </c>
       <c r="AM28" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN28" s="11"/>
       <c r="AO28" s="11"/>
       <c r="AP28"/>
       <c r="AQ28" s="17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AR28" s="17">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AS28" s="12" t="inlineStr">
         <is>
-          <t>Tetoria岸和田</t>
+          <t>セレクトショップHIKARI【インボイス対応店】</t>
         </is>
       </c>
       <c r="AT28" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU28" s="11" t="inlineStr">
@@ -13337,64 +13201,76 @@
       </c>
       <c r="AV28" s="12" t="inlineStr">
         <is>
-          <t>岸和田市 大阪府 5960006 JP</t>
+          <t>高知市 高知県 7810242 JP</t>
         </is>
       </c>
       <c r="AW28" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZHWG2831WCH8</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WEN0WQL6IM1B</t>
         </is>
       </c>
       <c r="AX28" s="11"/>
-      <c r="AY28" s="11"/>
+      <c r="AY28" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ28" s="11"/>
       <c r="BA28" s="11"/>
       <c r="BB28" s="11"/>
-      <c r="BC28" s="11"/>
+      <c r="BC28" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD28" s="11"/>
       <c r="BE28" s="11"/>
       <c r="BF28" s="11"/>
       <c r="BG28" s="11"/>
       <c r="BH28" s="12"/>
-      <c r="BI28" s="20"/>
+      <c r="BI28" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
       <c r="BJ28" s="20" t="inlineStr">
         <is>
-          <t>4.54 Kilograms</t>
+          <t>4.46 Kilograms</t>
         </is>
       </c>
       <c r="BK28" s="20" t="inlineStr">
         <is>
-          <t>4.54 kg</t>
+          <t>4.46 kg</t>
         </is>
       </c>
       <c r="BL28" s="20" t="inlineStr">
         <is>
-          <t>47.3 x 31.9 x 25 cm</t>
+          <t>38 x 25.4 x 26.3 cm</t>
         </is>
       </c>
       <c r="BM28" s="20" t="inlineStr">
         <is>
-          <t>47.30 x 31.90 x 25.00 cm</t>
+          <t>38.00 x 25.40 x 26.30 cm</t>
         </is>
       </c>
       <c r="BN28" s="20" t="inlineStr">
         <is>
-          <t>4.54 kg</t>
+          <t>4.95 kg</t>
         </is>
       </c>
       <c r="BO28" s="20" t="inlineStr">
         <is>
-          <t>4.54 kg</t>
+          <t>4.95 kg</t>
         </is>
       </c>
       <c r="BP28" s="20" t="inlineStr">
         <is>
-          <t>47.3 x 31.9 x 25 cm</t>
+          <t>49.4 x 29.5 x 25.6 cm</t>
         </is>
       </c>
       <c r="BQ28" s="20" t="inlineStr">
         <is>
-          <t>47.30 x 31.90 x 25.00 cm</t>
+          <t>49.40 x 29.50 x 25.60 cm</t>
         </is>
       </c>
       <c r="BR28" s="11" t="inlineStr">
@@ -13410,40 +13286,40 @@
       <c r="B29" s="11"/>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>B07GXPG63H</t>
+          <t>B0C6F9FBV1</t>
         </is>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>KÄRCHER</t>
+          <t>M Mistsince</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%82%B1%E3%83%AB%E3%83%92%E3%83%A3%E3%83%BCKARCHER/page/C3335239-5EF7-43A7-B432-CEBBBE4E3C9B?lp_asin=B07GXPG63H&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/Mistsince/page/D3BF9035-65AB-4860-9B3C-F101376ACA73?lp_asin=B0C6F9FBV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Karcher 蒸汽清洁器 SC2 EasyFix 1.512-059.0 清扫/除菌</t>
+          <t>Mistsince 蒸汽清洁器 蒸汽拖把 高温蒸汽吸尘器 带车床滑轨 450mL 蒸汽调节功能 水擦 轻量 紧凑 地板 油污 地毯 榻榻米 地板 大扫除</t>
         </is>
       </c>
       <c r="I29" s="12"/>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B07GXPG63H?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0C6F9FBV1?psc=1</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41H+7reLbSL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31Z+dPKeqqL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>B07GXPG63H</t>
+          <t>B0C6F9FBV1</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
@@ -13457,13 +13333,13 @@
         </is>
       </c>
       <c r="O29" s="13">
-        <v>49731</v>
+        <v>46595</v>
       </c>
       <c r="P29" s="13">
-        <v>35424</v>
+        <v>7611</v>
       </c>
       <c r="Q29" s="14">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="R29" s="15" t="inlineStr">
         <is>
@@ -13472,95 +13348,99 @@
       </c>
       <c r="S29" s="16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T29" s="13">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="U29" s="14">
-        <v>0.64</v>
+        <v>-0.12</v>
       </c>
       <c r="V29" s="13">
-        <v>846720</v>
-      </c>
-      <c r="W29" s="13"/>
-      <c r="X29" s="13"/>
+        <v>839055</v>
+      </c>
+      <c r="W29" s="13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X29" s="13">
+        <v>399550</v>
+      </c>
       <c r="Y29" s="17">
         <v>1</v>
       </c>
       <c r="Z29" s="13">
-        <v>18816</v>
+        <v>7991</v>
       </c>
       <c r="AA29"/>
       <c r="AB29"/>
-      <c r="AC29" s="2">
-        <v>18</v>
-      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" s="17">
-        <v>606</v>
+        <v>250</v>
       </c>
       <c r="AE29" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF29" s="18">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AG29" s="19">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="AH29" s="13">
-        <v>781</v>
+        <v>532</v>
       </c>
       <c r="AI29" s="14">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="AJ29"/>
       <c r="AK29" s="11" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AL29" s="17">
-        <v>2940</v>
+        <v>1219</v>
       </c>
       <c r="AM29" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN29" s="11"/>
       <c r="AO29" s="11"/>
       <c r="AP29"/>
       <c r="AQ29" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR29" s="17">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="AS29" s="12" t="inlineStr">
         <is>
-          <t>セレクトショップHIKARI【インボイス対応店】</t>
+          <t>Mistsince</t>
         </is>
       </c>
       <c r="AT29" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU29" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV29" s="12" t="inlineStr">
         <is>
-          <t>高知市 高知県 7810242 JP</t>
+          <t>Jiangsu 226511 CN</t>
         </is>
       </c>
       <c r="AW29" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WEN0WQL6IM1B</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AVZ7LMXDP1WK4</t>
         </is>
       </c>
       <c r="AX29" s="11"/>
@@ -13577,59 +13457,59 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD29" s="11"/>
+      <c r="BD29" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE29" s="11"/>
       <c r="BF29" s="11"/>
       <c r="BG29" s="11"/>
       <c r="BH29" s="12"/>
       <c r="BI29" s="20" t="inlineStr">
         <is>
-          <t>Amazon おすすめ</t>
+          <t>スチームクリーナー</t>
         </is>
       </c>
       <c r="BJ29" s="20" t="inlineStr">
         <is>
-          <t>4.46 Kilograms</t>
+          <t>2.76 Kilograms</t>
         </is>
       </c>
       <c r="BK29" s="20" t="inlineStr">
         <is>
-          <t>4.46 kg</t>
+          <t>2.76 kg</t>
         </is>
       </c>
       <c r="BL29" s="20" t="inlineStr">
         <is>
-          <t>38 x 25.4 x 26.3 cm</t>
-        </is>
-      </c>
-      <c r="BM29" s="20" t="inlineStr">
-        <is>
-          <t>38.00 x 25.40 x 26.30 cm</t>
-        </is>
-      </c>
+          <t>14奥行き x 30幅 x 115高さ cm</t>
+        </is>
+      </c>
+      <c r="BM29" s="20"/>
       <c r="BN29" s="20" t="inlineStr">
         <is>
-          <t>4.95 kg</t>
+          <t>2.76 kg</t>
         </is>
       </c>
       <c r="BO29" s="20" t="inlineStr">
         <is>
-          <t>4.95 kg</t>
+          <t>2.76 kg</t>
         </is>
       </c>
       <c r="BP29" s="20" t="inlineStr">
         <is>
-          <t>49.4 x 29.5 x 25.6 cm</t>
+          <t>43.3 x 33.4 x 15.4 cm</t>
         </is>
       </c>
       <c r="BQ29" s="20" t="inlineStr">
         <is>
-          <t>49.40 x 29.50 x 25.60 cm</t>
+          <t>43.30 x 33.40 x 15.40 cm</t>
         </is>
       </c>
       <c r="BR29" s="11" t="inlineStr">
         <is>
-          <t>大件</t>
+          <t>标准</t>
         </is>
       </c>
     </row>
@@ -13640,40 +13520,40 @@
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>B0C6F9FBV1</t>
+          <t>B0CLYBB2QG</t>
         </is>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="12"/>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>M Mistsince</t>
+          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Mistsince/page/D3BF9035-65AB-4860-9B3C-F101376ACA73?lp_asin=B0C6F9FBV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0CLYBB2QG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>Mistsince 蒸汽清洁器 蒸汽拖把 高温蒸汽吸尘器 带车床滑轨 450mL 蒸汽调节功能 水擦 轻量 紧凑 地板 油污 地毯 榻榻米 地板 大扫除</t>
+          <t>爱丽思欧雅玛 冲洗清洁器</t>
         </is>
       </c>
       <c r="I30" s="12"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0C6F9FBV1?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CLYBB2QG?psc=1</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31Z+dPKeqqL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31eHl3QohpL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>B0C6F9FBV1</t>
+          <t>B0CLYBB2QG</t>
         </is>
       </c>
       <c r="M30" s="12" t="inlineStr">
@@ -13687,13 +13567,13 @@
         </is>
       </c>
       <c r="O30" s="13">
-        <v>46595</v>
+        <v>37941</v>
       </c>
       <c r="P30" s="13">
-        <v>7611</v>
+        <v>-12835</v>
       </c>
       <c r="Q30" s="14">
-        <v>0.22</v>
+        <v>-0.28</v>
       </c>
       <c r="R30" s="15" t="inlineStr">
         <is>
@@ -13702,168 +13582,146 @@
       </c>
       <c r="S30" s="16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T30" s="13">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="U30" s="14">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="V30" s="13">
-        <v>839055</v>
-      </c>
-      <c r="W30" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X30" s="13">
-        <v>399550</v>
-      </c>
+        <v>795000</v>
+      </c>
+      <c r="W30" s="13"/>
+      <c r="X30" s="13"/>
       <c r="Y30" s="17">
         <v>1</v>
       </c>
       <c r="Z30" s="13">
-        <v>7991</v>
+        <v>15000</v>
       </c>
       <c r="AA30"/>
       <c r="AB30"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="17">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="AE30" s="13">
         <v>1</v>
       </c>
       <c r="AF30" s="18">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AG30" s="19">
-        <v>0.0095</v>
+        <v>0.0189</v>
       </c>
       <c r="AH30" s="13">
-        <v>532</v>
+        <v>675</v>
       </c>
       <c r="AI30" s="14">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AJ30"/>
       <c r="AK30" s="11" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="AL30" s="17">
-        <v>1219</v>
+        <v>1074</v>
       </c>
       <c r="AM30" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN30" s="11"/>
       <c r="AO30" s="11"/>
       <c r="AP30"/>
       <c r="AQ30" s="17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AR30" s="17">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="AS30" s="12" t="inlineStr">
         <is>
-          <t>Mistsince</t>
+          <t>あさんマーケット</t>
         </is>
       </c>
       <c r="AT30" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU30" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV30" s="12" t="inlineStr">
         <is>
-          <t>Jiangsu 226511 CN</t>
+          <t>滋賀県 5291647 JP</t>
         </is>
       </c>
       <c r="AW30" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AVZ7LMXDP1WK4</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WPB6AY1N585H</t>
         </is>
       </c>
       <c r="AX30" s="11"/>
-      <c r="AY30" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY30" s="11"/>
       <c r="AZ30" s="11"/>
       <c r="BA30" s="11"/>
       <c r="BB30" s="11"/>
-      <c r="BC30" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD30" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC30" s="11"/>
+      <c r="BD30" s="11"/>
       <c r="BE30" s="11"/>
       <c r="BF30" s="11"/>
       <c r="BG30" s="11"/>
       <c r="BH30" s="12"/>
-      <c r="BI30" s="20" t="inlineStr">
-        <is>
-          <t>スチームクリーナー</t>
-        </is>
-      </c>
+      <c r="BI30" s="20"/>
       <c r="BJ30" s="20" t="inlineStr">
         <is>
-          <t>2.76 Kilograms</t>
+          <t>2.5 Kilograms</t>
         </is>
       </c>
       <c r="BK30" s="20" t="inlineStr">
         <is>
-          <t>2.76 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL30" s="20" t="inlineStr">
         <is>
-          <t>14奥行き x 30幅 x 115高さ cm</t>
+          <t>32長さ x 8.8幅 x 20.5高さ cm</t>
         </is>
       </c>
       <c r="BM30" s="20"/>
       <c r="BN30" s="20" t="inlineStr">
         <is>
-          <t>2.76 kg</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BO30" s="20" t="inlineStr">
         <is>
-          <t>2.76 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BP30" s="20" t="inlineStr">
         <is>
-          <t>43.3 x 33.4 x 15.4 cm</t>
+          <t>43.1 x 24.3 x 20.2 cm</t>
         </is>
       </c>
       <c r="BQ30" s="20" t="inlineStr">
         <is>
-          <t>43.30 x 33.40 x 15.40 cm</t>
+          <t>43.10 x 24.30 x 20.20 cm</t>
         </is>
       </c>
       <c r="BR30" s="11" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>大件</t>
         </is>
       </c>
     </row>
@@ -13874,40 +13732,40 @@
       <c r="B31" s="11"/>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>B0CLYBB2QG</t>
+          <t>B0HK3489BN</t>
         </is>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="12"/>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
+          <t>Waitbird</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0CLYBB2QG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/Waitbird/page/3EF06D38-11FF-4AB3-B913-B77B78E9E2C6?lp_asin=B0HK3489BN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>爱丽思欧雅玛 冲洗清洁器</t>
+          <t>Waitbird ハンドスチームクリーナー 120℃高温蒸気除菌 4.5bar 高圧 21 点パーツs21 点アクセサリー付き｜4.5Bar 高圧｜5 分速熱｜1.1L 大容量タンク｜二重安全ロック｜薬剤不要 カーペット・ソファ・車内・マットレス</t>
         </is>
       </c>
       <c r="I31" s="12"/>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CLYBB2QG?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HK3489BN?psc=1</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31eHl3QohpL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41uxuzLFDeL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>B0CLYBB2QG</t>
+          <t>B0HK3489BN</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
@@ -13921,13 +13779,13 @@
         </is>
       </c>
       <c r="O31" s="13">
-        <v>37941</v>
+        <v>24098</v>
       </c>
       <c r="P31" s="13">
-        <v>-12835</v>
+        <v>5420</v>
       </c>
       <c r="Q31" s="14">
-        <v>-0.28</v>
+        <v>0.22</v>
       </c>
       <c r="R31" s="15" t="inlineStr">
         <is>
@@ -13936,141 +13794,151 @@
       </c>
       <c r="S31" s="16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="T31" s="13">
-        <v>53</v>
-      </c>
-      <c r="U31" s="14">
-        <v>-0.11</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="U31" s="14"/>
       <c r="V31" s="13">
-        <v>795000</v>
+        <v>769923</v>
       </c>
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
       <c r="Y31" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z31" s="13">
-        <v>15000</v>
+        <v>9999</v>
       </c>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="17">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="AE31" s="13">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="AF31" s="18">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="AG31" s="19">
-        <v>0.0189</v>
+        <v>0.3636</v>
       </c>
       <c r="AH31" s="13">
         <v>675</v>
       </c>
       <c r="AI31" s="14">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="AJ31"/>
       <c r="AK31" s="11" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AL31" s="17">
-        <v>1074</v>
+        <v>20</v>
       </c>
       <c r="AM31" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN31" s="11"/>
       <c r="AO31" s="11"/>
       <c r="AP31"/>
       <c r="AQ31" s="17">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AR31" s="17">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="AS31" s="12" t="inlineStr">
         <is>
-          <t>あさんマーケット</t>
+          <t>ngshizhaob</t>
         </is>
       </c>
       <c r="AT31" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU31" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV31" s="12" t="inlineStr">
         <is>
-          <t>滋賀県 5291647 JP</t>
+          <t>hefeishi anhuisheng 247001 CN</t>
         </is>
       </c>
       <c r="AW31" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WPB6AY1N585H</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3AAS2L1ZEPTML</t>
         </is>
       </c>
       <c r="AX31" s="11"/>
-      <c r="AY31" s="11"/>
+      <c r="AY31" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ31" s="11"/>
       <c r="BA31" s="11"/>
       <c r="BB31" s="11"/>
-      <c r="BC31" s="11"/>
-      <c r="BD31" s="11"/>
+      <c r="BC31" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD31" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE31" s="11"/>
       <c r="BF31" s="11"/>
       <c r="BG31" s="11"/>
       <c r="BH31" s="12"/>
-      <c r="BI31" s="20"/>
+      <c r="BI31" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
       <c r="BJ31" s="20" t="inlineStr">
         <is>
-          <t>2.5 Kilograms</t>
+          <t>4.5 Kilograms</t>
         </is>
       </c>
       <c r="BK31" s="20" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
-        </is>
-      </c>
-      <c r="BL31" s="20" t="inlineStr">
-        <is>
-          <t>32長さ x 8.8幅 x 20.5高さ cm</t>
-        </is>
-      </c>
+          <t>4.50 kg</t>
+        </is>
+      </c>
+      <c r="BL31" s="20"/>
       <c r="BM31" s="20"/>
       <c r="BN31" s="20" t="inlineStr">
         <is>
-          <t>2.5 kg</t>
+          <t>4.5 kg</t>
         </is>
       </c>
       <c r="BO31" s="20" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
+          <t>4.50 kg</t>
         </is>
       </c>
       <c r="BP31" s="20" t="inlineStr">
         <is>
-          <t>43.1 x 24.3 x 20.2 cm</t>
+          <t>52 x 28.5 x 18.5 cm</t>
         </is>
       </c>
       <c r="BQ31" s="20" t="inlineStr">
         <is>
-          <t>43.10 x 24.30 x 20.20 cm</t>
+          <t>52.00 x 28.50 x 18.50 cm</t>
         </is>
       </c>
       <c r="BR31" s="11" t="inlineStr">
@@ -14086,40 +13954,40 @@
       <c r="B32" s="11"/>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>B0HK3489BN</t>
+          <t>B0GGY1Y4CK</t>
         </is>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="12"/>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>Waitbird</t>
+          <t>TOKAIZ</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Waitbird/page/3EF06D38-11FF-4AB3-B913-B77B78E9E2C6?lp_asin=B0HK3489BN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/TOKAIZ/page/9CAE01F0-2A50-4674-BB57-A53225F3A5EA?lp_asin=B0GGY1Y4CK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Waitbird ハンドスチームクリーナー 120℃高温蒸気除菌 4.5bar 高圧 21 点パーツs21 点アクセサリー付き｜4.5Bar 高圧｜5 分速熱｜1.1L 大容量タンク｜二重安全ロック｜薬剤不要 カーペット・ソファ・車内・マットレス</t>
+          <t>TOKAIZ 2026年最新 织物清洁剂 Favro 100℃ 蒸汽 地毯清洁剂 18,000Pa 强力吸力 温水清洗 4档温度切换 日语语音指南 蒸汽清洁器 1台2用 沙发 布清洗机 车内清洁 TCE-FC Pro</t>
         </is>
       </c>
       <c r="I32" s="12"/>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HK3489BN?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GGY1Y4CK?psc=1</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41uxuzLFDeL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/413QwzNv1IL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>B0HK3489BN</t>
+          <t>B0GGY1Y4CK</t>
         </is>
       </c>
       <c r="M32" s="12" t="inlineStr">
@@ -14133,13 +14001,13 @@
         </is>
       </c>
       <c r="O32" s="13">
-        <v>24098</v>
+        <v>68961</v>
       </c>
       <c r="P32" s="13">
-        <v>5420</v>
+        <v>-29501</v>
       </c>
       <c r="Q32" s="14">
-        <v>0.22</v>
+        <v>-0.16</v>
       </c>
       <c r="R32" s="15" t="inlineStr">
         <is>
@@ -14148,99 +14016,97 @@
       </c>
       <c r="S32" s="16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T32" s="13">
-        <v>77</v>
-      </c>
-      <c r="U32" s="14"/>
+        <v>32</v>
+      </c>
+      <c r="U32" s="14">
+        <v>-0.38</v>
+      </c>
       <c r="V32" s="13">
-        <v>769923</v>
+        <v>761600</v>
       </c>
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
       <c r="Y32" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z32" s="13">
-        <v>9999</v>
+        <v>23800</v>
       </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="17">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="AE32" s="13">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AF32" s="18">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="AG32" s="19">
-        <v>0.3636</v>
+        <v>0</v>
       </c>
       <c r="AH32" s="13">
-        <v>675</v>
+        <v>781</v>
       </c>
       <c r="AI32" s="14">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="AJ32"/>
       <c r="AK32" s="11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AL32" s="17">
-        <v>20</v>
+        <v>265</v>
       </c>
       <c r="AM32" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN32" s="11"/>
       <c r="AO32" s="11"/>
       <c r="AP32"/>
       <c r="AQ32" s="17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR32" s="17">
         <v>2</v>
       </c>
       <c r="AS32" s="12" t="inlineStr">
         <is>
-          <t>ngshizhaob</t>
+          <t>TOKAIZ（トカイズ）公式ストア</t>
         </is>
       </c>
       <c r="AT32" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU32" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV32" s="12" t="inlineStr">
         <is>
-          <t>hefeishi anhuisheng 247001 CN</t>
+          <t>船橋市 千葉県 2730011 JP</t>
         </is>
       </c>
       <c r="AW32" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3AAS2L1ZEPTML</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A249HMDQ0OTKWV</t>
         </is>
       </c>
       <c r="AX32" s="11"/>
-      <c r="AY32" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY32" s="11"/>
       <c r="AZ32" s="11"/>
       <c r="BA32" s="11"/>
       <c r="BB32" s="11"/>
@@ -14258,11 +14124,7 @@
       <c r="BF32" s="11"/>
       <c r="BG32" s="11"/>
       <c r="BH32" s="12"/>
-      <c r="BI32" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
+      <c r="BI32" s="20"/>
       <c r="BJ32" s="20" t="inlineStr">
         <is>
           <t>4.5 Kilograms</t>
@@ -14273,26 +14135,30 @@
           <t>4.50 kg</t>
         </is>
       </c>
-      <c r="BL32" s="20"/>
+      <c r="BL32" s="20" t="inlineStr">
+        <is>
+          <t>23.8奥行き x 33.5幅 x 32高さ cm</t>
+        </is>
+      </c>
       <c r="BM32" s="20"/>
       <c r="BN32" s="20" t="inlineStr">
         <is>
-          <t>4.5 kg</t>
+          <t>7.11 kg</t>
         </is>
       </c>
       <c r="BO32" s="20" t="inlineStr">
         <is>
-          <t>4.50 kg</t>
+          <t>7.11 kg</t>
         </is>
       </c>
       <c r="BP32" s="20" t="inlineStr">
         <is>
-          <t>52 x 28.5 x 18.5 cm</t>
+          <t>45.7 x 39.2 x 28.8 cm</t>
         </is>
       </c>
       <c r="BQ32" s="20" t="inlineStr">
         <is>
-          <t>52.00 x 28.50 x 18.50 cm</t>
+          <t>45.70 x 39.20 x 28.80 cm</t>
         </is>
       </c>
       <c r="BR32" s="11" t="inlineStr">
@@ -14308,40 +14174,40 @@
       <c r="B33" s="11"/>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>B0GGY1Y4CK</t>
+          <t>B0H8SPVHVZ</t>
         </is>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>TOKAIZ</t>
+          <t>evove</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/TOKAIZ/page/9CAE01F0-2A50-4674-BB57-A53225F3A5EA?lp_asin=B0GGY1Y4CK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%81%8D%E3%82%8C%E3%81%84%E3%81%AE%E6%99%82%E9%96%93%E3%82%92%E3%80%81%E7%A7%81%E3%81%AE%E6%99%82%E9%96%93%E3%81%AB%E3%80%82/page/B441CACF-20A2-4071-9530-2CC8DA3A24B6?lp_asin=B0H8SPVHVZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>TOKAIZ 2026年最新 织物清洁剂 Favro 100℃ 蒸汽 地毯清洁剂 18,000Pa 强力吸力 温水清洗 4档温度切换 日语语音指南 蒸汽清洁器 1台2用 沙发 布清洗机 车内清洁 TCE-FC Pro</t>
+          <t>evove [12秒速热・大容量水箱] evove 蒸汽清洁器 120℃高温 高压 手持式 1500W 除菌率99.9% 水箱1250毫升 附带8种喷嘴 油污 宠物 婴儿 玩具 年末清洁 SC01</t>
         </is>
       </c>
       <c r="I33" s="12"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GGY1Y4CK?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H8SPVHVZ?psc=1</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/413QwzNv1IL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/418sjd-uV7L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>B0GGY1Y4CK</t>
+          <t>B0H8SPVHVZ</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
@@ -14355,13 +14221,13 @@
         </is>
       </c>
       <c r="O33" s="13">
-        <v>68961</v>
+        <v>51531</v>
       </c>
       <c r="P33" s="13">
-        <v>-29501</v>
+        <v>52753</v>
       </c>
       <c r="Q33" s="14">
-        <v>-0.16</v>
+        <v>0.59</v>
       </c>
       <c r="R33" s="15" t="inlineStr">
         <is>
@@ -14370,17 +14236,17 @@
       </c>
       <c r="S33" s="16" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T33" s="13">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="U33" s="14">
-        <v>-0.38</v>
+        <v>-0.03</v>
       </c>
       <c r="V33" s="13">
-        <v>761600</v>
+        <v>663917</v>
       </c>
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
@@ -14388,75 +14254,75 @@
         <v>1</v>
       </c>
       <c r="Z33" s="13">
-        <v>23800</v>
+        <v>7999</v>
       </c>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="17">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE33" s="13">
         <v>0</v>
       </c>
       <c r="AF33" s="18">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG33" s="19">
         <v>0</v>
       </c>
       <c r="AH33" s="13">
-        <v>781</v>
+        <v>472</v>
       </c>
       <c r="AI33" s="14">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="AJ33"/>
       <c r="AK33" s="11" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AL33" s="17">
-        <v>265</v>
+        <v>37</v>
       </c>
       <c r="AM33" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN33" s="11"/>
       <c r="AO33" s="11"/>
       <c r="AP33"/>
       <c r="AQ33" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR33" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS33" s="12" t="inlineStr">
         <is>
-          <t>TOKAIZ（トカイズ）公式ストア</t>
+          <t>EVOVE</t>
         </is>
       </c>
       <c r="AT33" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU33" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV33" s="12" t="inlineStr">
         <is>
-          <t>船橋市 千葉県 2730011 JP</t>
+          <t>紅磡 九龍 999077 HK</t>
         </is>
       </c>
       <c r="AW33" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A249HMDQ0OTKWV</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3WKMH8N8T04I</t>
         </is>
       </c>
       <c r="AX33" s="11"/>
@@ -14481,43 +14347,47 @@
       <c r="BI33" s="20"/>
       <c r="BJ33" s="20" t="inlineStr">
         <is>
-          <t>4.5 Kilograms</t>
+          <t>1.97 Kilograms</t>
         </is>
       </c>
       <c r="BK33" s="20" t="inlineStr">
         <is>
-          <t>4.50 kg</t>
+          <t>1.97 kg</t>
         </is>
       </c>
       <c r="BL33" s="20" t="inlineStr">
         <is>
-          <t>23.8奥行き x 33.5幅 x 32高さ cm</t>
-        </is>
-      </c>
-      <c r="BM33" s="20"/>
+          <t>17.3 x 13.5 x 21.5 cm</t>
+        </is>
+      </c>
+      <c r="BM33" s="20" t="inlineStr">
+        <is>
+          <t>17.30 x 13.50 x 21.50 cm</t>
+        </is>
+      </c>
       <c r="BN33" s="20" t="inlineStr">
         <is>
-          <t>7.11 kg</t>
+          <t>1.97 kg</t>
         </is>
       </c>
       <c r="BO33" s="20" t="inlineStr">
         <is>
-          <t>7.11 kg</t>
+          <t>1.97 kg</t>
         </is>
       </c>
       <c r="BP33" s="20" t="inlineStr">
         <is>
-          <t>45.7 x 39.2 x 28.8 cm</t>
+          <t>28.4 x 21.8 x 17.9 cm</t>
         </is>
       </c>
       <c r="BQ33" s="20" t="inlineStr">
         <is>
-          <t>45.70 x 39.20 x 28.80 cm</t>
+          <t>28.40 x 21.80 x 17.90 cm</t>
         </is>
       </c>
       <c r="BR33" s="11" t="inlineStr">
         <is>
-          <t>大件</t>
+          <t>标准</t>
         </is>
       </c>
     </row>
@@ -14528,7 +14398,7 @@
       <c r="B34" s="11"/>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>B0H8SPVHVZ</t>
+          <t>B0GCCPG7M6</t>
         </is>
       </c>
       <c r="D34" s="12"/>
@@ -14540,28 +14410,28 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%81%8D%E3%82%8C%E3%81%84%E3%81%AE%E6%99%82%E9%96%93%E3%82%92%E3%80%81%E7%A7%81%E3%81%AE%E6%99%82%E9%96%93%E3%81%AB%E3%80%82/page/B441CACF-20A2-4071-9530-2CC8DA3A24B6?lp_asin=B0H8SPVHVZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%81%8D%E3%82%8C%E3%81%84%E3%81%AE%E6%99%82%E9%96%93%E3%82%92%E3%80%81%E7%A7%81%E3%81%AE%E6%99%82%E9%96%93%E3%81%AB%E3%80%82/page/B441CACF-20A2-4071-9530-2CC8DA3A24B6?lp_asin=B0GCCPG7M6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>evove [12秒速热・大容量水箱] evove 蒸汽清洁器 120℃高温 高压 手持式 1500W 除菌率99.9% 水箱1250毫升 附带8种喷嘴 油污 宠物 婴儿 玩具 年末清洁 SC01</t>
+          <t>[12秒速热/大容量水箱] evove 蒸汽清洁器 120℃ 高温 高压 手持式 1500W 除菌率99.9% 水箱1250毫升 附带8种喷嘴 厨房 油污 宠物 婴儿 玩具 年末清洁 SC01</t>
         </is>
       </c>
       <c r="I34" s="12"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H8SPVHVZ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GCCPG7M6?psc=1</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/418sjd-uV7L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41YsUtHrVDL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
-          <t>B0H8SPVHVZ</t>
+          <t>B0GCCPG7M6</t>
         </is>
       </c>
       <c r="M34" s="12" t="inlineStr">
@@ -14575,13 +14445,13 @@
         </is>
       </c>
       <c r="O34" s="13">
-        <v>51531</v>
+        <v>58748</v>
       </c>
       <c r="P34" s="13">
-        <v>52753</v>
+        <v>-14316</v>
       </c>
       <c r="Q34" s="14">
-        <v>0.59</v>
+        <v>-0.32</v>
       </c>
       <c r="R34" s="15" t="inlineStr">
         <is>
@@ -14590,37 +14460,43 @@
       </c>
       <c r="S34" s="16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T34" s="13">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="U34" s="14">
-        <v>-0.03</v>
+        <v>-0.27</v>
       </c>
       <c r="V34" s="13">
-        <v>663917</v>
-      </c>
-      <c r="W34" s="13"/>
-      <c r="X34" s="13"/>
+        <v>633504</v>
+      </c>
+      <c r="W34" s="13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X34" s="13">
+        <v>325917</v>
+      </c>
       <c r="Y34" s="17">
         <v>1</v>
       </c>
       <c r="Z34" s="13">
-        <v>7999</v>
+        <v>6599</v>
       </c>
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="17">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE34" s="13">
         <v>0</v>
       </c>
       <c r="AF34" s="18">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="AG34" s="19">
         <v>0</v>
@@ -14629,16 +14505,16 @@
         <v>472</v>
       </c>
       <c r="AI34" s="14">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="AJ34"/>
       <c r="AK34" s="11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AL34" s="17">
-        <v>37</v>
+        <v>221</v>
       </c>
       <c r="AM34" s="11" t="inlineStr">
         <is>
@@ -14649,10 +14525,10 @@
       <c r="AO34" s="11"/>
       <c r="AP34"/>
       <c r="AQ34" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR34" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS34" s="12" t="inlineStr">
         <is>
@@ -14680,7 +14556,11 @@
         </is>
       </c>
       <c r="AX34" s="11"/>
-      <c r="AY34" s="11"/>
+      <c r="AY34" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ34" s="11"/>
       <c r="BA34" s="11"/>
       <c r="BB34" s="11"/>
@@ -14698,45 +14578,49 @@
       <c r="BF34" s="11"/>
       <c r="BG34" s="11"/>
       <c r="BH34" s="12"/>
-      <c r="BI34" s="20"/>
+      <c r="BI34" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
       <c r="BJ34" s="20" t="inlineStr">
         <is>
-          <t>1.97 Kilograms</t>
+          <t>2.22 Kilograms</t>
         </is>
       </c>
       <c r="BK34" s="20" t="inlineStr">
         <is>
-          <t>1.97 kg</t>
+          <t>2.22 kg</t>
         </is>
       </c>
       <c r="BL34" s="20" t="inlineStr">
         <is>
-          <t>17.3 x 13.5 x 21.5 cm</t>
+          <t>15.5 x 13 x 24.2 cm</t>
         </is>
       </c>
       <c r="BM34" s="20" t="inlineStr">
         <is>
-          <t>17.30 x 13.50 x 21.50 cm</t>
+          <t>15.50 x 13.00 x 24.20 cm</t>
         </is>
       </c>
       <c r="BN34" s="20" t="inlineStr">
         <is>
-          <t>1.97 kg</t>
+          <t>2.22 kg</t>
         </is>
       </c>
       <c r="BO34" s="20" t="inlineStr">
         <is>
-          <t>1.97 kg</t>
+          <t>2.22 kg</t>
         </is>
       </c>
       <c r="BP34" s="20" t="inlineStr">
         <is>
-          <t>28.4 x 21.8 x 17.9 cm</t>
+          <t>30.3 x 21.8 x 17.6 cm</t>
         </is>
       </c>
       <c r="BQ34" s="20" t="inlineStr">
         <is>
-          <t>28.40 x 21.80 x 17.90 cm</t>
+          <t>30.30 x 21.80 x 17.60 cm</t>
         </is>
       </c>
       <c r="BR34" s="11" t="inlineStr">
@@ -14752,40 +14636,40 @@
       <c r="B35" s="11"/>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>B0GCCPG7M6</t>
+          <t>B0GF8HHWYQ</t>
         </is>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="12"/>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>evove</t>
+          <t>M Mistsince</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%81%8D%E3%82%8C%E3%81%84%E3%81%AE%E6%99%82%E9%96%93%E3%82%92%E3%80%81%E7%A7%81%E3%81%AE%E6%99%82%E9%96%93%E3%81%AB%E3%80%82/page/B441CACF-20A2-4071-9530-2CC8DA3A24B6?lp_asin=B0GCCPG7M6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/Mistsince/page/D3BF9035-65AB-4860-9B3C-F101376ACA73?lp_asin=B0GF8HHWYQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>[12秒速热/大容量水箱] evove 蒸汽清洁器 120℃ 高温 高压 手持式 1500W 除菌率99.9% 水箱1250毫升 附带8种喷嘴 厨房 油污 宠物 婴儿 玩具 年末清洁 SC01</t>
+          <t>Mistsince 蒸汽清洁器 手持式 15件套 高压蒸汽清洗 轻量型 家用 便携式 厨房清洁 浴室清洁 榻榻米 油污 水垢 年末清洁 除菌</t>
         </is>
       </c>
       <c r="I35" s="12"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GCCPG7M6?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GF8HHWYQ?psc=1</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41YsUtHrVDL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61u2zZZEngL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>B0GCCPG7M6</t>
+          <t>B0GF8HHWYQ</t>
         </is>
       </c>
       <c r="M35" s="12" t="inlineStr">
@@ -14799,13 +14683,13 @@
         </is>
       </c>
       <c r="O35" s="13">
-        <v>58748</v>
+        <v>21954</v>
       </c>
       <c r="P35" s="13">
-        <v>-14316</v>
+        <v>20514</v>
       </c>
       <c r="Q35" s="14">
-        <v>-0.32</v>
+        <v>0.48</v>
       </c>
       <c r="R35" s="15" t="inlineStr">
         <is>
@@ -14814,17 +14698,17 @@
       </c>
       <c r="S35" s="16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T35" s="13">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="U35" s="14">
-        <v>-0.27</v>
+        <v>-0.47</v>
       </c>
       <c r="V35" s="13">
-        <v>633504</v>
+        <v>546552</v>
       </c>
       <c r="W35" s="13" t="inlineStr">
         <is>
@@ -14832,43 +14716,43 @@
         </is>
       </c>
       <c r="X35" s="13">
-        <v>325917</v>
+        <v>363507</v>
       </c>
       <c r="Y35" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z35" s="13">
-        <v>6599</v>
+        <v>7591</v>
       </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="17">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AE35" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF35" s="18">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AG35" s="19">
-        <v>0</v>
+        <v>0.0278</v>
       </c>
       <c r="AH35" s="13">
         <v>472</v>
       </c>
       <c r="AI35" s="14">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AL35" s="17">
-        <v>221</v>
+        <v>172</v>
       </c>
       <c r="AM35" s="11" t="inlineStr">
         <is>
@@ -14879,14 +14763,14 @@
       <c r="AO35" s="11"/>
       <c r="AP35"/>
       <c r="AQ35" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR35" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS35" s="12" t="inlineStr">
         <is>
-          <t>EVOVE</t>
+          <t>Mistsince</t>
         </is>
       </c>
       <c r="AT35" s="11" t="inlineStr">
@@ -14896,17 +14780,17 @@
       </c>
       <c r="AU35" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV35" s="12" t="inlineStr">
         <is>
-          <t>紅磡 九龍 999077 HK</t>
+          <t>Jiangsu 226511 CN</t>
         </is>
       </c>
       <c r="AW35" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3WKMH8N8T04I</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AVZ7LMXDP1WK4</t>
         </is>
       </c>
       <c r="AX35" s="11"/>
@@ -14939,42 +14823,38 @@
       </c>
       <c r="BJ35" s="20" t="inlineStr">
         <is>
-          <t>2.22 Kilograms</t>
+          <t>2.55 Kilograms</t>
         </is>
       </c>
       <c r="BK35" s="20" t="inlineStr">
         <is>
-          <t>2.22 kg</t>
+          <t>2.55 kg</t>
         </is>
       </c>
       <c r="BL35" s="20" t="inlineStr">
         <is>
-          <t>15.5 x 13 x 24.2 cm</t>
-        </is>
-      </c>
-      <c r="BM35" s="20" t="inlineStr">
-        <is>
-          <t>15.50 x 13.00 x 24.20 cm</t>
-        </is>
-      </c>
+          <t>10奥行き x 20幅 x 10高さ cm</t>
+        </is>
+      </c>
+      <c r="BM35" s="20"/>
       <c r="BN35" s="20" t="inlineStr">
         <is>
-          <t>2.22 kg</t>
+          <t>2.55 kg</t>
         </is>
       </c>
       <c r="BO35" s="20" t="inlineStr">
         <is>
-          <t>2.22 kg</t>
+          <t>2.55 kg</t>
         </is>
       </c>
       <c r="BP35" s="20" t="inlineStr">
         <is>
-          <t>30.3 x 21.8 x 17.6 cm</t>
+          <t>39.8 x 24.9 x 13.6 cm</t>
         </is>
       </c>
       <c r="BQ35" s="20" t="inlineStr">
         <is>
-          <t>30.30 x 21.80 x 17.60 cm</t>
+          <t>39.80 x 24.90 x 13.60 cm</t>
         </is>
       </c>
       <c r="BR35" s="11" t="inlineStr">
@@ -14990,40 +14870,40 @@
       <c r="B36" s="11"/>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>B0GF8HHWYQ</t>
+          <t>B0B3XBM5HW</t>
         </is>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="12"/>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>M Mistsince</t>
+          <t>KÄRCHER</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Mistsince/page/D3BF9035-65AB-4860-9B3C-F101376ACA73?lp_asin=B0GF8HHWYQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.jp/stores/%E3%82%B1%E3%83%AB%E3%83%92%E3%83%A3%E3%83%BCKARCHER/page/C3335239-5EF7-43A7-B432-CEBBBE4E3C9B?lp_asin=B0B3XBM5HW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>Mistsince 蒸汽清洁器 手持式 15件套 高压蒸汽清洗 轻量型 家用 便携式 厨房清洁 浴室清洁 榻榻米 油污 水垢 年末清洁 除菌</t>
+          <t>凯尔欣（Karcher）蒸汽清洁器 SC MINI 适合日常小型使用的紧凑型号 便携 轻量 高温稳定的蒸汽锅炉加热 浮起顽固污垢 只用水消毒除臭 油污 地毯 干净地板 水垢 厨房 浴室 玄关 厕所 车 衣物 配件齐全 选配配件丰富 1.516-339</t>
         </is>
       </c>
       <c r="I36" s="12"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GF8HHWYQ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0B3XBM5HW?psc=1</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61u2zZZEngL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51Sf-O7BUfL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
-          <t>B0GF8HHWYQ</t>
+          <t>B0B3XBM5HW</t>
         </is>
       </c>
       <c r="M36" s="12" t="inlineStr">
@@ -15037,13 +14917,13 @@
         </is>
       </c>
       <c r="O36" s="13">
-        <v>21954</v>
+        <v>49718</v>
       </c>
       <c r="P36" s="13">
-        <v>20514</v>
+        <v>21402</v>
       </c>
       <c r="Q36" s="14">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="R36" s="15" t="inlineStr">
         <is>
@@ -15052,61 +14932,55 @@
       </c>
       <c r="S36" s="16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="T36" s="13">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="U36" s="14">
-        <v>-0.47</v>
+        <v>-0.34</v>
       </c>
       <c r="V36" s="13">
-        <v>546552</v>
-      </c>
-      <c r="W36" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X36" s="13">
-        <v>363507</v>
-      </c>
+        <v>242520</v>
+      </c>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
       <c r="Y36" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z36" s="13">
-        <v>7591</v>
+        <v>5640</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="17">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AE36" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF36" s="18">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="AG36" s="19">
-        <v>0.0278</v>
+        <v>0</v>
       </c>
       <c r="AH36" s="13">
         <v>472</v>
       </c>
       <c r="AI36" s="14">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="11" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AL36" s="17">
-        <v>172</v>
+        <v>1577</v>
       </c>
       <c r="AM36" s="11" t="inlineStr">
         <is>
@@ -15117,14 +14991,14 @@
       <c r="AO36" s="11"/>
       <c r="AP36"/>
       <c r="AQ36" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR36" s="17">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AS36" s="12" t="inlineStr">
         <is>
-          <t>Mistsince</t>
+          <t>Genki市場ドットコム</t>
         </is>
       </c>
       <c r="AT36" s="11" t="inlineStr">
@@ -15134,81 +15008,65 @@
       </c>
       <c r="AU36" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV36" s="12" t="inlineStr">
         <is>
-          <t>Jiangsu 226511 CN</t>
+          <t>埼玉県 3380812 JP</t>
         </is>
       </c>
       <c r="AW36" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AVZ7LMXDP1WK4</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AWJMS00CHSZRT</t>
         </is>
       </c>
       <c r="AX36" s="11"/>
-      <c r="AY36" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY36" s="11"/>
       <c r="AZ36" s="11"/>
       <c r="BA36" s="11"/>
       <c r="BB36" s="11"/>
-      <c r="BC36" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD36" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC36" s="11"/>
+      <c r="BD36" s="11"/>
       <c r="BE36" s="11"/>
       <c r="BF36" s="11"/>
       <c r="BG36" s="11"/>
       <c r="BH36" s="12"/>
-      <c r="BI36" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
+      <c r="BI36" s="20"/>
       <c r="BJ36" s="20" t="inlineStr">
         <is>
-          <t>2.55 Kilograms</t>
+          <t>1.6 Kilograms</t>
         </is>
       </c>
       <c r="BK36" s="20" t="inlineStr">
         <is>
-          <t>2.55 kg</t>
+          <t>1.60 kg</t>
         </is>
       </c>
       <c r="BL36" s="20" t="inlineStr">
         <is>
-          <t>10奥行き x 20幅 x 10高さ cm</t>
+          <t>35 x 321 x 127 x 186 mm</t>
         </is>
       </c>
       <c r="BM36" s="20"/>
       <c r="BN36" s="20" t="inlineStr">
         <is>
-          <t>2.55 kg</t>
+          <t>2.11 kg</t>
         </is>
       </c>
       <c r="BO36" s="20" t="inlineStr">
         <is>
-          <t>2.55 kg</t>
+          <t>2.11 kg</t>
         </is>
       </c>
       <c r="BP36" s="20" t="inlineStr">
         <is>
-          <t>39.8 x 24.9 x 13.6 cm</t>
+          <t>35.9 x 19.3 x 14.5 cm</t>
         </is>
       </c>
       <c r="BQ36" s="20" t="inlineStr">
         <is>
-          <t>39.80 x 24.90 x 13.60 cm</t>
+          <t>35.90 x 19.30 x 14.50 cm</t>
         </is>
       </c>
       <c r="BR36" s="11" t="inlineStr">
@@ -15224,40 +15082,40 @@
       <c r="B37" s="11"/>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>B0B3XBM5HW</t>
+          <t>B0FC4YLXC2</t>
         </is>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="12"/>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>KÄRCHER</t>
+          <t>Yoquna</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%82%B1%E3%83%AB%E3%83%92%E3%83%A3%E3%83%BCKARCHER/page/C3335239-5EF7-43A7-B432-CEBBBE4E3C9B?lp_asin=B0B3XBM5HW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/Yoquna/page/506291FF-A2EF-4B20-AEA8-C1DC1422EAEA?lp_asin=B0FC4YLXC2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>凯尔欣（Karcher）蒸汽清洁器 SC MINI 适合日常小型使用的紧凑型号 便携 轻量 高温稳定的蒸汽锅炉加热 浮起顽固污垢 只用水消毒除臭 油污 地毯 干净地板 水垢 厨房 浴室 玄关 厕所 车 衣物 配件齐全 选配配件丰富 1.516-339</t>
+          <t>Yoquna 地毯清洁剂 60℃ 温水生成 100℃蒸汽 淋水吸尘器 蒸汽清洁器 窗帘 沙发 厨房床垫 高温清洗 强力吸力 大容量水箱 日语指导 铺垫 地毯 蒸汽 清洁器 厨房垫</t>
         </is>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0B3XBM5HW?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FC4YLXC2?psc=1</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51Sf-O7BUfL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41z81OFfyxL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>B0B3XBM5HW</t>
+          <t>B0FC4YLXC2</t>
         </is>
       </c>
       <c r="M37" s="12" t="inlineStr">
@@ -15271,13 +15129,13 @@
         </is>
       </c>
       <c r="O37" s="13">
-        <v>49718</v>
+        <v>69461</v>
       </c>
       <c r="P37" s="13">
-        <v>21402</v>
+        <v>3248</v>
       </c>
       <c r="Q37" s="14">
-        <v>0.52</v>
+        <v>0.04</v>
       </c>
       <c r="R37" s="15" t="inlineStr">
         <is>
@@ -15286,17 +15144,17 @@
       </c>
       <c r="S37" s="16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T37" s="13">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="U37" s="14">
-        <v>-0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="V37" s="13">
-        <v>242520</v>
+        <v>220830</v>
       </c>
       <c r="W37" s="13"/>
       <c r="X37" s="13"/>
@@ -15304,60 +15162,58 @@
         <v>1</v>
       </c>
       <c r="Z37" s="13">
-        <v>5640</v>
+        <v>12990</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="17">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AE37" s="13">
         <v>0</v>
       </c>
       <c r="AF37" s="18">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AG37" s="19">
         <v>0</v>
       </c>
-      <c r="AH37" s="13">
-        <v>472</v>
-      </c>
+      <c r="AH37" s="13"/>
       <c r="AI37" s="14">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="11" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AL37" s="17">
-        <v>1577</v>
+        <v>489</v>
       </c>
       <c r="AM37" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN37" s="11"/>
       <c r="AO37" s="11"/>
       <c r="AP37"/>
       <c r="AQ37" s="17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR37" s="17">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AS37" s="12" t="inlineStr">
         <is>
-          <t>Genki市場ドットコム</t>
+          <t>Mailo-Shop (毎日朝と14時締め 当日2回出荷)</t>
         </is>
       </c>
       <c r="AT37" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU37" s="11" t="inlineStr">
@@ -15367,12 +15223,12 @@
       </c>
       <c r="AV37" s="12" t="inlineStr">
         <is>
-          <t>埼玉県 3380812 JP</t>
+          <t>東大阪市 大阪府 5770805 JP</t>
         </is>
       </c>
       <c r="AW37" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AWJMS00CHSZRT</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3KBWI6Y9WW9KR</t>
         </is>
       </c>
       <c r="AX37" s="11"/>
@@ -15380,54 +15236,34 @@
       <c r="AZ37" s="11"/>
       <c r="BA37" s="11"/>
       <c r="BB37" s="11"/>
-      <c r="BC37" s="11"/>
-      <c r="BD37" s="11"/>
+      <c r="BC37" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD37" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE37" s="11"/>
       <c r="BF37" s="11"/>
       <c r="BG37" s="11"/>
       <c r="BH37" s="12"/>
       <c r="BI37" s="20"/>
-      <c r="BJ37" s="20" t="inlineStr">
-        <is>
-          <t>1.6 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK37" s="20" t="inlineStr">
-        <is>
-          <t>1.60 kg</t>
-        </is>
-      </c>
+      <c r="BJ37" s="20"/>
+      <c r="BK37" s="20"/>
       <c r="BL37" s="20" t="inlineStr">
         <is>
-          <t>35 x 321 x 127 x 186 mm</t>
+          <t>26奥行き x 32幅 x 40高さ cm</t>
         </is>
       </c>
       <c r="BM37" s="20"/>
-      <c r="BN37" s="20" t="inlineStr">
-        <is>
-          <t>2.11 kg</t>
-        </is>
-      </c>
-      <c r="BO37" s="20" t="inlineStr">
-        <is>
-          <t>2.11 kg</t>
-        </is>
-      </c>
-      <c r="BP37" s="20" t="inlineStr">
-        <is>
-          <t>35.9 x 19.3 x 14.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ37" s="20" t="inlineStr">
-        <is>
-          <t>35.90 x 19.30 x 14.50 cm</t>
-        </is>
-      </c>
-      <c r="BR37" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
+      <c r="BN37" s="20"/>
+      <c r="BO37" s="20"/>
+      <c r="BP37" s="20"/>
+      <c r="BQ37" s="20"/>
+      <c r="BR37" s="11"/>
     </row>
     <row r="38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
@@ -15436,40 +15272,40 @@
       <c r="B38" s="11"/>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>B0FC4YLXC2</t>
+          <t>B0HBNN64GG</t>
         </is>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="12"/>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>Yoquna</t>
+          <t>PROSTREET</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Yoquna/page/506291FF-A2EF-4B20-AEA8-C1DC1422EAEA?lp_asin=B0FC4YLXC2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=PROSTREET</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>Yoquna 地毯清洁剂 60℃ 温水生成 100℃蒸汽 淋水吸尘器 蒸汽清洁器 窗帘 沙发 厨房床垫 高温清洗 强力吸力 大容量水箱 日语指导 铺垫 地毯 蒸汽 清洁器 厨房垫</t>
+          <t>[SNS上热门话题] New PROSTREET Steam Rinser Cleaner Pro Street 60摄氏度 温水 100摄氏度 蒸汽 清洁器 吸尘器 j汽车清洁剂 地毯清洁器 窗帘 沙发 厨房 床垫 车 高温清洗 强力吸力 大容量水</t>
         </is>
       </c>
       <c r="I38" s="12"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FC4YLXC2?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HBNN64GG?psc=1</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41z81OFfyxL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/412-JGnvDBL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>B0FC4YLXC2</t>
+          <t>B0HBNN64GG</t>
         </is>
       </c>
       <c r="M38" s="12" t="inlineStr">
@@ -15483,13 +15319,13 @@
         </is>
       </c>
       <c r="O38" s="13">
-        <v>69461</v>
+        <v>60773</v>
       </c>
       <c r="P38" s="13">
-        <v>3248</v>
+        <v>-18914</v>
       </c>
       <c r="Q38" s="14">
-        <v>0.04</v>
+        <v>-0.17</v>
       </c>
       <c r="R38" s="15" t="inlineStr">
         <is>
@@ -15498,17 +15334,15 @@
       </c>
       <c r="S38" s="16" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T38" s="13">
-        <v>17</v>
-      </c>
-      <c r="U38" s="14">
-        <v>-0.4</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="U38" s="14"/>
       <c r="V38" s="13">
-        <v>220830</v>
+        <v>140000</v>
       </c>
       <c r="W38" s="13"/>
       <c r="X38" s="13"/>
@@ -15516,58 +15350,60 @@
         <v>1</v>
       </c>
       <c r="Z38" s="13">
-        <v>12990</v>
+        <v>14000</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="17">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE38" s="13">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AF38" s="18">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AG38" s="19">
         <v>0</v>
       </c>
-      <c r="AH38" s="13"/>
+      <c r="AH38" s="13">
+        <v>781</v>
+      </c>
       <c r="AI38" s="14">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AJ38"/>
       <c r="AK38" s="11" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AL38" s="17">
-        <v>489</v>
+        <v>52</v>
       </c>
       <c r="AM38" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN38" s="11"/>
       <c r="AO38" s="11"/>
       <c r="AP38"/>
       <c r="AQ38" s="17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AR38" s="17">
         <v>1</v>
       </c>
       <c r="AS38" s="12" t="inlineStr">
         <is>
-          <t>Mailo-Shop (毎日朝と14時締め 当日2回出荷)</t>
+          <t>株式会社PROSTREET</t>
         </is>
       </c>
       <c r="AT38" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU38" s="11" t="inlineStr">
@@ -15577,47 +15413,79 @@
       </c>
       <c r="AV38" s="12" t="inlineStr">
         <is>
-          <t>東大阪市 大阪府 5770805 JP</t>
+          <t>大阪府 5918007 JP</t>
         </is>
       </c>
       <c r="AW38" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3KBWI6Y9WW9KR</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YO7910ANGPIW</t>
         </is>
       </c>
       <c r="AX38" s="11"/>
-      <c r="AY38" s="11"/>
+      <c r="AY38" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ38" s="11"/>
       <c r="BA38" s="11"/>
       <c r="BB38" s="11"/>
-      <c r="BC38" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD38" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC38" s="11"/>
+      <c r="BD38" s="11"/>
       <c r="BE38" s="11"/>
       <c r="BF38" s="11"/>
       <c r="BG38" s="11"/>
       <c r="BH38" s="12"/>
-      <c r="BI38" s="20"/>
-      <c r="BJ38" s="20"/>
-      <c r="BK38" s="20"/>
+      <c r="BI38" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
+      <c r="BJ38" s="20" t="inlineStr">
+        <is>
+          <t>6.2 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK38" s="20" t="inlineStr">
+        <is>
+          <t>6.20 kg</t>
+        </is>
+      </c>
       <c r="BL38" s="20" t="inlineStr">
         <is>
-          <t>26奥行き x 32幅 x 40高さ cm</t>
-        </is>
-      </c>
-      <c r="BM38" s="20"/>
-      <c r="BN38" s="20"/>
-      <c r="BO38" s="20"/>
-      <c r="BP38" s="20"/>
-      <c r="BQ38" s="20"/>
-      <c r="BR38" s="11"/>
+          <t>26 x 32 x 40 cm</t>
+        </is>
+      </c>
+      <c r="BM38" s="20" t="inlineStr">
+        <is>
+          <t>26.00 x 32.00 x 40.00 cm</t>
+        </is>
+      </c>
+      <c r="BN38" s="20" t="inlineStr">
+        <is>
+          <t>6.2 kg</t>
+        </is>
+      </c>
+      <c r="BO38" s="20" t="inlineStr">
+        <is>
+          <t>6.20 kg</t>
+        </is>
+      </c>
+      <c r="BP38" s="20" t="inlineStr">
+        <is>
+          <t>41 x 37.5 x 30.8 cm</t>
+        </is>
+      </c>
+      <c r="BQ38" s="20" t="inlineStr">
+        <is>
+          <t>41.00 x 37.50 x 30.80 cm</t>
+        </is>
+      </c>
+      <c r="BR38" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
@@ -15626,40 +15494,40 @@
       <c r="B39" s="11"/>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>B0HBNN64GG</t>
+          <t>B0HC9N8LCH</t>
         </is>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>PROSTREET</t>
+          <t>G-KiKi</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=PROSTREET</t>
+          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=G-KiKi</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>[SNS上热门话题] New PROSTREET Steam Rinser Cleaner Pro Street 60摄氏度 温水 100摄氏度 蒸汽 清洁器 吸尘器 j汽车清洁剂 地毯清洁器 窗帘 沙发 厨房 床垫 车 高温清洗 强力吸力 大容量水</t>
+          <t>蒸汽冲洗器 1台4用 干湿两用 大容量双水箱 语音导览 旋转脚轮 小巧收纳 适用于地毯、沙发、床垫、车内座椅</t>
         </is>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HBNN64GG?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HC9N8LCH?psc=1</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/412-JGnvDBL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51CZtGWw4AL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>B0HBNN64GG</t>
+          <t>B0HC9N8LCH</t>
         </is>
       </c>
       <c r="M39" s="12" t="inlineStr">
@@ -15673,13 +15541,11 @@
         </is>
       </c>
       <c r="O39" s="13">
-        <v>60773</v>
-      </c>
-      <c r="P39" s="13">
-        <v>-18914</v>
-      </c>
+        <v>47440</v>
+      </c>
+      <c r="P39" s="13"/>
       <c r="Q39" s="14">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="R39" s="15" t="inlineStr">
         <is>
@@ -15688,15 +15554,15 @@
       </c>
       <c r="S39" s="16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T39" s="13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U39" s="14"/>
       <c r="V39" s="13">
-        <v>140000</v>
+        <v>139860</v>
       </c>
       <c r="W39" s="13"/>
       <c r="X39" s="13"/>
@@ -15704,19 +15570,19 @@
         <v>1</v>
       </c>
       <c r="Z39" s="13">
-        <v>14000</v>
+        <v>19980</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="17">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="AE39" s="13">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AF39" s="18">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AG39" s="19">
         <v>0</v>
@@ -15725,16 +15591,16 @@
         <v>781</v>
       </c>
       <c r="AI39" s="14">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AL39" s="17">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="AM39" s="11" t="inlineStr">
         <is>
@@ -15745,14 +15611,14 @@
       <c r="AO39" s="11"/>
       <c r="AP39"/>
       <c r="AQ39" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR39" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS39" s="12" t="inlineStr">
         <is>
-          <t>株式会社PROSTREET</t>
+          <t>GKK公式直営・安心保証</t>
         </is>
       </c>
       <c r="AT39" s="11" t="inlineStr">
@@ -15762,17 +15628,17 @@
       </c>
       <c r="AU39" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV39" s="12" t="inlineStr">
         <is>
-          <t>大阪府 5918007 JP</t>
+          <t>娄底市 湖南 417000 CN</t>
         </is>
       </c>
       <c r="AW39" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YO7910ANGPIW</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A15YNDSRCB68XM</t>
         </is>
       </c>
       <c r="AX39" s="11"/>
@@ -15784,8 +15650,16 @@
       <c r="AZ39" s="11"/>
       <c r="BA39" s="11"/>
       <c r="BB39" s="11"/>
-      <c r="BC39" s="11"/>
-      <c r="BD39" s="11"/>
+      <c r="BC39" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD39" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE39" s="11"/>
       <c r="BF39" s="11"/>
       <c r="BG39" s="11"/>
@@ -15797,42 +15671,34 @@
       </c>
       <c r="BJ39" s="20" t="inlineStr">
         <is>
-          <t>6.2 Kilograms</t>
+          <t>6.8 Kilograms</t>
         </is>
       </c>
       <c r="BK39" s="20" t="inlineStr">
         <is>
-          <t>6.20 kg</t>
-        </is>
-      </c>
-      <c r="BL39" s="20" t="inlineStr">
-        <is>
-          <t>26 x 32 x 40 cm</t>
-        </is>
-      </c>
-      <c r="BM39" s="20" t="inlineStr">
-        <is>
-          <t>26.00 x 32.00 x 40.00 cm</t>
-        </is>
-      </c>
+          <t>6.80 kg</t>
+        </is>
+      </c>
+      <c r="BL39" s="20"/>
+      <c r="BM39" s="20"/>
       <c r="BN39" s="20" t="inlineStr">
         <is>
-          <t>6.2 kg</t>
+          <t>6.8 kg</t>
         </is>
       </c>
       <c r="BO39" s="20" t="inlineStr">
         <is>
-          <t>6.20 kg</t>
+          <t>6.80 kg</t>
         </is>
       </c>
       <c r="BP39" s="20" t="inlineStr">
         <is>
-          <t>41 x 37.5 x 30.8 cm</t>
+          <t>42.9 x 35.8 x 31.6 cm</t>
         </is>
       </c>
       <c r="BQ39" s="20" t="inlineStr">
         <is>
-          <t>41.00 x 37.50 x 30.80 cm</t>
+          <t>42.90 x 35.80 x 31.60 cm</t>
         </is>
       </c>
       <c r="BR39" s="11" t="inlineStr">
@@ -15848,40 +15714,40 @@
       <c r="B40" s="11"/>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>B0HC9N8LCH</t>
+          <t>B0HKYTFSJD</t>
         </is>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="12"/>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>G-KiKi</t>
+          <t>TopDuterpick</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=G-KiKi</t>
+          <t>https://www.amazon.co.jp/TopDuterpick/b/ref=bl_dp_s_web_8448083051?ie=UTF8&amp;node=8448083051&amp;field-lbr_brands_browse-bin=TopDuterpick</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>蒸汽冲洗器 1台4用 干湿两用 大容量双水箱 语音导览 旋转脚轮 小巧收纳 适用于地毯、沙发、床垫、车内座椅</t>
+          <t>蒸汽清洁器【100℃蒸汽喷射×19000Pa吸力】 地毯清洁剂 冲洗清洁剂 2900毫升 水箱 90平方米的清洁范围 加热式 地毯清洗机 去污 沙发清洁剂 地毯清洁剂 水洗 车用清洁 真空吸尘器 干湿两用 床垫/布制品/宠物座椅/车内/地毯/沙发/毛</t>
         </is>
       </c>
       <c r="I40" s="12"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HC9N8LCH?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HKYTFSJD?psc=1</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51CZtGWw4AL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41srV4Bdl3L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>B0HC9N8LCH</t>
+          <t>B0HKYTFSJD</t>
         </is>
       </c>
       <c r="M40" s="12" t="inlineStr">
@@ -15895,7 +15761,7 @@
         </is>
       </c>
       <c r="O40" s="13">
-        <v>47440</v>
+        <v>56074</v>
       </c>
       <c r="P40" s="13"/>
       <c r="Q40" s="14">
@@ -15908,7 +15774,7 @@
       </c>
       <c r="S40" s="16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T40" s="13">
@@ -15916,7 +15782,7 @@
       </c>
       <c r="U40" s="14"/>
       <c r="V40" s="13">
-        <v>139860</v>
+        <v>116193</v>
       </c>
       <c r="W40" s="13"/>
       <c r="X40" s="13"/>
@@ -15924,7 +15790,7 @@
         <v>1</v>
       </c>
       <c r="Z40" s="13">
-        <v>19980</v>
+        <v>16599</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
@@ -15936,13 +15802,13 @@
         <v>0</v>
       </c>
       <c r="AF40" s="18">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AG40" s="19">
         <v>0</v>
       </c>
       <c r="AH40" s="13">
-        <v>781</v>
+        <v>675</v>
       </c>
       <c r="AI40" s="14">
         <v>0.81</v>
@@ -15950,11 +15816,11 @@
       <c r="AJ40"/>
       <c r="AK40" s="11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AL40" s="17">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AM40" s="11" t="inlineStr">
         <is>
@@ -15965,14 +15831,14 @@
       <c r="AO40" s="11"/>
       <c r="AP40"/>
       <c r="AQ40" s="17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR40" s="17">
         <v>2</v>
       </c>
       <c r="AS40" s="12" t="inlineStr">
         <is>
-          <t>GKK公式直営・安心保証</t>
+          <t>Duter</t>
         </is>
       </c>
       <c r="AT40" s="11" t="inlineStr">
@@ -15982,25 +15848,21 @@
       </c>
       <c r="AU40" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV40" s="12" t="inlineStr">
         <is>
-          <t>娄底市 湖南 417000 CN</t>
+          <t>京都市 6128379 JP</t>
         </is>
       </c>
       <c r="AW40" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A15YNDSRCB68XM</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A18CF0AX3KZRVX</t>
         </is>
       </c>
       <c r="AX40" s="11"/>
-      <c r="AY40" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY40" s="11"/>
       <c r="AZ40" s="11"/>
       <c r="BA40" s="11"/>
       <c r="BB40" s="11"/>
@@ -16018,41 +15880,41 @@
       <c r="BF40" s="11"/>
       <c r="BG40" s="11"/>
       <c r="BH40" s="12"/>
-      <c r="BI40" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
+      <c r="BI40" s="20"/>
       <c r="BJ40" s="20" t="inlineStr">
         <is>
-          <t>6.8 Kilograms</t>
+          <t>3.5 Kilograms</t>
         </is>
       </c>
       <c r="BK40" s="20" t="inlineStr">
         <is>
-          <t>6.80 kg</t>
-        </is>
-      </c>
-      <c r="BL40" s="20"/>
+          <t>3.50 kg</t>
+        </is>
+      </c>
+      <c r="BL40" s="20" t="inlineStr">
+        <is>
+          <t>25奥行き x 25幅 x 45高さ cm</t>
+        </is>
+      </c>
       <c r="BM40" s="20"/>
       <c r="BN40" s="20" t="inlineStr">
         <is>
-          <t>6.8 kg</t>
+          <t>3.5 kg</t>
         </is>
       </c>
       <c r="BO40" s="20" t="inlineStr">
         <is>
-          <t>6.80 kg</t>
+          <t>3.50 kg</t>
         </is>
       </c>
       <c r="BP40" s="20" t="inlineStr">
         <is>
-          <t>42.9 x 35.8 x 31.6 cm</t>
+          <t>38 x 35 x 24 cm</t>
         </is>
       </c>
       <c r="BQ40" s="20" t="inlineStr">
         <is>
-          <t>42.90 x 35.80 x 31.60 cm</t>
+          <t>38.00 x 35.00 x 24.00 cm</t>
         </is>
       </c>
       <c r="BR40" s="11" t="inlineStr">
@@ -16068,40 +15930,40 @@
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>B0F4KNH1MF</t>
+          <t>B0HHM96S2L</t>
         </is>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="12"/>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>bumxca</t>
+          <t>udodik</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/bumxca%EF%BC%88%E3%83%90%E3%83%A0%E3%82%B9%E3%82%AB%EF%BC%89%E7%9B%B4%E5%96%B6%E5%85%AC%E5%BC%8F%E5%BA%97/page/EB7E5050-7292-4C62-8EA5-D1F993EEFD10?lp_asin=B0F4KNH1MF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/udodik/b/ref=bl_dp_s_web_21106953051?ie=UTF8&amp;node=21106953051&amp;field-lbr_brands_browse-bin=udodik</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>bumxca 蒸汽清洁器 蒸汽吸尘器 【手柄带蒸汽开关】强力1500W 4.5BAR高压 12S速热 搭载LED显示屏s温度和蒸汽量二合一消毒/除菌/除螨 1.2L大容量 110V 105℃~120℃ steam cleaner 厨房/厨房/空调</t>
+          <t>Udodik 蒸汽清洁器是一款家用便携式蒸汽清洁器,配有 10 件配件套装,可用于各种表面,天然材料,不含化学物。家庭、厨房、汽车、地毯、年终清洁等。</t>
         </is>
       </c>
       <c r="I41" s="12"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0F4KNH1MF?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HHM96S2L?psc=1</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51r9znyHJXL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41C7wf1aFFL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>B0F4KNH1MF</t>
+          <t>B0HHM96S2L</t>
         </is>
       </c>
       <c r="M41" s="12" t="inlineStr">
@@ -16115,13 +15977,13 @@
         </is>
       </c>
       <c r="O41" s="13">
-        <v>42308</v>
+        <v>57570</v>
       </c>
       <c r="P41" s="13">
-        <v>-161454</v>
+        <v>116268</v>
       </c>
       <c r="Q41" s="14">
-        <v>-3.05</v>
+        <v>0.67</v>
       </c>
       <c r="R41" s="15" t="inlineStr">
         <is>
@@ -16130,17 +15992,15 @@
       </c>
       <c r="S41" s="16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T41" s="13">
-        <v>22</v>
-      </c>
-      <c r="U41" s="14">
-        <v>0.35</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="U41" s="14"/>
       <c r="V41" s="13">
-        <v>125378</v>
+        <v>93086</v>
       </c>
       <c r="W41" s="13"/>
       <c r="X41" s="13"/>
@@ -16148,37 +16008,37 @@
         <v>1</v>
       </c>
       <c r="Z41" s="13">
-        <v>5699</v>
+        <v>6649</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="17">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AE41" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF41" s="18">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="AG41" s="19">
-        <v>0.0455</v>
+        <v>0.1429</v>
       </c>
       <c r="AH41" s="13">
         <v>472</v>
       </c>
       <c r="AI41" s="14">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="11" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AL41" s="17">
-        <v>541</v>
+        <v>34</v>
       </c>
       <c r="AM41" s="11" t="inlineStr">
         <is>
@@ -16189,14 +16049,14 @@
       <c r="AO41" s="11"/>
       <c r="AP41"/>
       <c r="AQ41" s="17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AR41" s="17">
         <v>1</v>
       </c>
       <c r="AS41" s="12" t="inlineStr">
         <is>
-          <t>bumxca（バムスカ）直営公式店</t>
+          <t>jinanrenxianchengxinxikejiyouxiangongsi</t>
         </is>
       </c>
       <c r="AT41" s="11" t="inlineStr">
@@ -16206,17 +16066,17 @@
       </c>
       <c r="AU41" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV41" s="12" t="inlineStr">
         <is>
-          <t>HONG KONG 999077 HK</t>
+          <t>济南市 山东 250100 CN</t>
         </is>
       </c>
       <c r="AW41" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AW2A52M1BCKPL</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3LLGXOKFXGBZY</t>
         </is>
       </c>
       <c r="AX41" s="11"/>
@@ -16224,16 +16084,8 @@
       <c r="AZ41" s="11"/>
       <c r="BA41" s="11"/>
       <c r="BB41" s="11"/>
-      <c r="BC41" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD41" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC41" s="11"/>
+      <c r="BD41" s="11"/>
       <c r="BE41" s="11"/>
       <c r="BF41" s="11"/>
       <c r="BG41" s="11"/>
@@ -16241,43 +16093,39 @@
       <c r="BI41" s="20"/>
       <c r="BJ41" s="20" t="inlineStr">
         <is>
-          <t>1.78 Kilograms</t>
+          <t>2.08 Kilograms</t>
         </is>
       </c>
       <c r="BK41" s="20" t="inlineStr">
         <is>
-          <t>1.78 kg</t>
-        </is>
-      </c>
-      <c r="BL41" s="20" t="inlineStr">
-        <is>
-          <t>37 x 37 x 17 x 21 cm</t>
-        </is>
-      </c>
+          <t>2.08 kg</t>
+        </is>
+      </c>
+      <c r="BL41" s="20"/>
       <c r="BM41" s="20"/>
       <c r="BN41" s="20" t="inlineStr">
         <is>
-          <t>1.78 kg</t>
+          <t>2.08 kg</t>
         </is>
       </c>
       <c r="BO41" s="20" t="inlineStr">
         <is>
-          <t>1.78 kg</t>
+          <t>2.08 kg</t>
         </is>
       </c>
       <c r="BP41" s="20" t="inlineStr">
         <is>
-          <t>27.2 x 21 x 17.2 cm</t>
+          <t>27.3 x 26.5 x 20 cm</t>
         </is>
       </c>
       <c r="BQ41" s="20" t="inlineStr">
         <is>
-          <t>27.20 x 21.00 x 17.20 cm</t>
+          <t>27.30 x 26.50 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR41" s="11" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>大件</t>
         </is>
       </c>
     </row>
@@ -16288,214 +16136,104 @@
       <c r="B42" s="11"/>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>B0HKYTFSJD</t>
+          <t>B0151FQ7PU</t>
         </is>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="12"/>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>TopDuterpick</t>
-        </is>
-      </c>
+      <c r="F42" s="12"/>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/TopDuterpick/b/ref=bl_dp_s_web_8448083051?ie=UTF8&amp;node=8448083051&amp;field-lbr_brands_browse-bin=TopDuterpick</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>蒸汽清洁器【100℃蒸汽喷射×19000Pa吸力】 地毯清洁剂 冲洗清洁剂 2900毫升 水箱 90平方米的清洁范围 加热式 地毯清洗机 去污 沙发清洁剂 地毯清洁剂 水洗 车用清洁 真空吸尘器 干湿两用 床垫/布制品/宠物座椅/车内/地毯/沙发/毛</t>
+          <t>H2O 蒸汽FX 8件豪华套装 (绿色)</t>
         </is>
       </c>
       <c r="I42" s="12"/>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HKYTFSJD?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0151FQ7PU?psc=1</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41srV4Bdl3L._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61LMfetbCwL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
-          <t>B0HKYTFSJD</t>
-        </is>
-      </c>
-      <c r="M42" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン:家電:生活家電:スチームクリーナー</t>
-        </is>
-      </c>
-      <c r="N42" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン</t>
-        </is>
-      </c>
-      <c r="O42" s="13">
-        <v>56074</v>
-      </c>
+          <t>B0151FQ7PU</t>
+        </is>
+      </c>
+      <c r="M42" s="12"/>
+      <c r="N42" s="12"/>
+      <c r="O42" s="13"/>
       <c r="P42" s="13"/>
-      <c r="Q42" s="14">
-        <v>0</v>
-      </c>
-      <c r="R42" s="15" t="inlineStr">
-        <is>
-          <t>スチームクリーナー</t>
-        </is>
-      </c>
-      <c r="S42" s="16" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="T42" s="13">
-        <v>7</v>
-      </c>
+      <c r="Q42" s="14"/>
+      <c r="R42" s="15"/>
+      <c r="S42" s="16"/>
+      <c r="T42" s="13"/>
       <c r="U42" s="14"/>
-      <c r="V42" s="13">
-        <v>116193</v>
-      </c>
+      <c r="V42" s="13"/>
       <c r="W42" s="13"/>
       <c r="X42" s="13"/>
-      <c r="Y42" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z42" s="13">
-        <v>16599</v>
-      </c>
+      <c r="Y42" s="17"/>
+      <c r="Z42" s="13"/>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="17">
+        <v>423</v>
+      </c>
+      <c r="AE42" s="13"/>
+      <c r="AF42" s="18">
         <v>3</v>
-      </c>
-      <c r="AE42" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="18">
-        <v>4.6</v>
       </c>
       <c r="AG42" s="19">
         <v>0</v>
       </c>
-      <c r="AH42" s="13">
-        <v>675</v>
-      </c>
+      <c r="AH42" s="13"/>
       <c r="AI42" s="14">
-        <v>0.81</v>
+        <v>0</v>
       </c>
       <c r="AJ42"/>
-      <c r="AK42" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="AL42" s="17">
-        <v>11</v>
-      </c>
-      <c r="AM42" s="11" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK42" s="11"/>
+      <c r="AL42" s="17"/>
+      <c r="AM42" s="11"/>
       <c r="AN42" s="11"/>
       <c r="AO42" s="11"/>
       <c r="AP42"/>
-      <c r="AQ42" s="17">
-        <v>7</v>
-      </c>
-      <c r="AR42" s="17">
-        <v>2</v>
-      </c>
-      <c r="AS42" s="12" t="inlineStr">
-        <is>
-          <t>Duter</t>
-        </is>
-      </c>
-      <c r="AT42" s="11" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU42" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV42" s="12" t="inlineStr">
-        <is>
-          <t>京都市 6128379 JP</t>
-        </is>
-      </c>
-      <c r="AW42" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A18CF0AX3KZRVX</t>
-        </is>
-      </c>
+      <c r="AQ42" s="17"/>
+      <c r="AR42" s="17"/>
+      <c r="AS42" s="12"/>
+      <c r="AT42" s="11"/>
+      <c r="AU42" s="11"/>
+      <c r="AV42" s="12"/>
+      <c r="AW42" s="11"/>
       <c r="AX42" s="11"/>
       <c r="AY42" s="11"/>
       <c r="AZ42" s="11"/>
       <c r="BA42" s="11"/>
       <c r="BB42" s="11"/>
-      <c r="BC42" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD42" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC42" s="11"/>
+      <c r="BD42" s="11"/>
       <c r="BE42" s="11"/>
       <c r="BF42" s="11"/>
       <c r="BG42" s="11"/>
       <c r="BH42" s="12"/>
       <c r="BI42" s="20"/>
-      <c r="BJ42" s="20" t="inlineStr">
-        <is>
-          <t>3.5 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK42" s="20" t="inlineStr">
-        <is>
-          <t>3.50 kg</t>
-        </is>
-      </c>
-      <c r="BL42" s="20" t="inlineStr">
-        <is>
-          <t>25奥行き x 25幅 x 45高さ cm</t>
-        </is>
-      </c>
+      <c r="BJ42" s="20"/>
+      <c r="BK42" s="20"/>
+      <c r="BL42" s="20"/>
       <c r="BM42" s="20"/>
-      <c r="BN42" s="20" t="inlineStr">
-        <is>
-          <t>3.5 kg</t>
-        </is>
-      </c>
-      <c r="BO42" s="20" t="inlineStr">
-        <is>
-          <t>3.50 kg</t>
-        </is>
-      </c>
-      <c r="BP42" s="20" t="inlineStr">
-        <is>
-          <t>38 x 35 x 24 cm</t>
-        </is>
-      </c>
-      <c r="BQ42" s="20" t="inlineStr">
-        <is>
-          <t>38.00 x 35.00 x 24.00 cm</t>
-        </is>
-      </c>
-      <c r="BR42" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN42" s="20"/>
+      <c r="BO42" s="20"/>
+      <c r="BP42" s="20"/>
+      <c r="BQ42" s="20"/>
+      <c r="BR42" s="11"/>
     </row>
     <row r="43" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
@@ -16504,228 +16242,104 @@
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>B08R3LF57P</t>
+          <t>B09JJLTTX3</t>
         </is>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>KEEPOW</t>
-        </is>
-      </c>
+      <c r="F43" s="12"/>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/KEEPOW/page/21523984-F72B-4ED5-8C28-45B0588E2513?lp_asin=B08R3LF57P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>KEEPOW 8枚組 ケルヒャー用 消耗品 スチームクリーナー ハンドブラシ用sマイクロファイバーカバー SC用アクセサリー 部品 付属品 イージーフィックスパーツ 非純正</t>
+          <t>ケルヒャー(KARCHER) 蒸汽拖把 SC Upright 1.513-349.0</t>
         </is>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B08R3LF57P?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B09JJLTTX3?psc=1</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41AHQ4cHR8L._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/41s1gdhaMXL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>B08R3LF57P</t>
-        </is>
-      </c>
-      <c r="M43" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン:家電:生活家電:スチームクリーナー</t>
-        </is>
-      </c>
-      <c r="N43" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン</t>
-        </is>
-      </c>
-      <c r="O43" s="13">
-        <v>56686</v>
-      </c>
-      <c r="P43" s="13">
-        <v>-3609</v>
-      </c>
-      <c r="Q43" s="14">
-        <v>-0.05</v>
-      </c>
-      <c r="R43" s="15" t="inlineStr">
-        <is>
-          <t>スチームクリーナー</t>
-        </is>
-      </c>
-      <c r="S43" s="16" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="T43" s="13">
-        <v>42</v>
-      </c>
+          <t>B09JJLTTX3</t>
+        </is>
+      </c>
+      <c r="M43" s="12"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="14"/>
+      <c r="R43" s="15"/>
+      <c r="S43" s="16"/>
+      <c r="T43" s="13"/>
       <c r="U43" s="14"/>
-      <c r="V43" s="13">
-        <v>96558</v>
-      </c>
+      <c r="V43" s="13"/>
       <c r="W43" s="13"/>
       <c r="X43" s="13"/>
-      <c r="Y43" s="17">
-        <v>4</v>
-      </c>
-      <c r="Z43" s="13">
-        <v>2299</v>
-      </c>
+      <c r="Y43" s="17"/>
+      <c r="Z43" s="13"/>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="17">
-        <v>263</v>
-      </c>
-      <c r="AE43" s="13">
-        <v>2</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="AE43" s="13"/>
       <c r="AF43" s="18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AG43" s="19">
-        <v>0.047599999999999996</v>
-      </c>
-      <c r="AH43" s="13">
-        <v>318</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH43" s="13"/>
       <c r="AI43" s="14">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AJ43"/>
-      <c r="AK43" s="11" t="inlineStr">
-        <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="AL43" s="17">
-        <v>2044</v>
-      </c>
-      <c r="AM43" s="11" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK43" s="11"/>
+      <c r="AL43" s="17"/>
+      <c r="AM43" s="11"/>
       <c r="AN43" s="11"/>
       <c r="AO43" s="11"/>
       <c r="AP43"/>
-      <c r="AQ43" s="17">
-        <v>8</v>
-      </c>
-      <c r="AR43" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS43" s="12" t="inlineStr">
-        <is>
-          <t>Roberts Robot</t>
-        </is>
-      </c>
-      <c r="AT43" s="11" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU43" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV43" s="12" t="inlineStr">
-        <is>
-          <t>Guangzhou Guangdong 511442 CN</t>
-        </is>
-      </c>
-      <c r="AW43" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A30T80D6SCTMYZ</t>
-        </is>
-      </c>
+      <c r="AQ43" s="17"/>
+      <c r="AR43" s="17"/>
+      <c r="AS43" s="12"/>
+      <c r="AT43" s="11"/>
+      <c r="AU43" s="11"/>
+      <c r="AV43" s="12"/>
+      <c r="AW43" s="11"/>
       <c r="AX43" s="11"/>
-      <c r="AY43" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY43" s="11"/>
       <c r="AZ43" s="11"/>
       <c r="BA43" s="11"/>
       <c r="BB43" s="11"/>
-      <c r="BC43" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD43" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC43" s="11"/>
+      <c r="BD43" s="11"/>
       <c r="BE43" s="11"/>
       <c r="BF43" s="11"/>
       <c r="BG43" s="11"/>
       <c r="BH43" s="12"/>
-      <c r="BI43" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
-      <c r="BJ43" s="20" t="inlineStr">
-        <is>
-          <t>190 g</t>
-        </is>
-      </c>
-      <c r="BK43" s="20" t="inlineStr">
-        <is>
-          <t>190.00 g</t>
-        </is>
-      </c>
-      <c r="BL43" s="20" t="inlineStr">
-        <is>
-          <t>22.5 x 20.3 x 2.8 cm</t>
-        </is>
-      </c>
-      <c r="BM43" s="20" t="inlineStr">
-        <is>
-          <t>22.50 x 20.30 x 2.80 cm</t>
-        </is>
-      </c>
-      <c r="BN43" s="20" t="inlineStr">
-        <is>
-          <t>190 g</t>
-        </is>
-      </c>
-      <c r="BO43" s="20" t="inlineStr">
-        <is>
-          <t>190.00 g</t>
-        </is>
-      </c>
-      <c r="BP43" s="20" t="inlineStr">
-        <is>
-          <t>22.5 x 20.3 x 2.8 cm</t>
-        </is>
-      </c>
-      <c r="BQ43" s="20" t="inlineStr">
-        <is>
-          <t>22.50 x 20.30 x 2.80 cm</t>
-        </is>
-      </c>
-      <c r="BR43" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
+      <c r="BI43" s="20"/>
+      <c r="BJ43" s="20"/>
+      <c r="BK43" s="20"/>
+      <c r="BL43" s="20"/>
+      <c r="BM43" s="20"/>
+      <c r="BN43" s="20"/>
+      <c r="BO43" s="20"/>
+      <c r="BP43" s="20"/>
+      <c r="BQ43" s="20"/>
+      <c r="BR43" s="11"/>
     </row>
     <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
@@ -16734,230 +16348,106 @@
       <c r="B44" s="11"/>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>B0DRCGRJSR</t>
+          <t>B0CZ3TPQLS</t>
         </is>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="12"/>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>HAUSHOF</t>
-        </is>
-      </c>
+      <c r="F44" s="12"/>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0DRCGRJSR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>HAUSHOF スチームクリーナー 小型 スチーム掃除機 高温スチームクリーナー ボイラー式加熱 8ピースアタッチメントを備えた ハンディ スチーム洗浄機 100% 天然清掃 化学薬品を一切使用せず 家庭/キッチン/自動車/スチームクリーニング/カー</t>
+          <t>【24年新发布】 凯希（Karcher）蒸汽清洁器 SC2 EasyFix W 标准型 高温稳定蒸汽锅炉加热 浮起顽固污渍 仅用水消毒除臭 地板清洁 油污 地毯 干爽地板 水垢 厨房 浴室 玄关 厕所 车辆 衣物 配件齐全 选配配件丰富 1.512-</t>
         </is>
       </c>
       <c r="I44" s="12"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DRCGRJSR?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CZ3TPQLS?psc=1</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41wLqF+bzbL._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51f3q63b8bL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>B0DRCGRJSR</t>
-        </is>
-      </c>
-      <c r="M44" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン:家電:生活家電:スチームクリーナー</t>
-        </is>
-      </c>
-      <c r="N44" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン</t>
-        </is>
-      </c>
-      <c r="O44" s="13">
-        <v>29392</v>
-      </c>
-      <c r="P44" s="13">
-        <v>65796</v>
-      </c>
-      <c r="Q44" s="14">
-        <v>0.69</v>
-      </c>
-      <c r="R44" s="15" t="inlineStr">
-        <is>
-          <t>スチームクリーナー</t>
-        </is>
-      </c>
-      <c r="S44" s="16" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="T44" s="13">
-        <v>16</v>
-      </c>
-      <c r="U44" s="14">
-        <v>-0.97</v>
-      </c>
-      <c r="V44" s="13">
-        <v>95680</v>
-      </c>
+          <t>B0CZ3TPQLS</t>
+        </is>
+      </c>
+      <c r="M44" s="12"/>
+      <c r="N44" s="12"/>
+      <c r="O44" s="13"/>
+      <c r="P44" s="13"/>
+      <c r="Q44" s="14"/>
+      <c r="R44" s="15"/>
+      <c r="S44" s="16"/>
+      <c r="T44" s="13"/>
+      <c r="U44" s="14"/>
+      <c r="V44" s="13"/>
       <c r="W44" s="13"/>
       <c r="X44" s="13"/>
-      <c r="Y44" s="17">
-        <v>2</v>
-      </c>
+      <c r="Y44" s="17"/>
       <c r="Z44" s="13">
-        <v>5980</v>
+        <v>147</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="17">
-        <v>219</v>
-      </c>
-      <c r="AE44" s="13">
+        <v>59</v>
+      </c>
+      <c r="AE44" s="13"/>
+      <c r="AF44" s="18">
         <v>4</v>
       </c>
-      <c r="AF44" s="18">
-        <v>4.1</v>
-      </c>
       <c r="AG44" s="19">
-        <v>0.25</v>
-      </c>
-      <c r="AH44" s="13">
-        <v>472</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH44" s="13"/>
       <c r="AI44" s="14">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="AJ44"/>
-      <c r="AK44" s="11" t="inlineStr">
-        <is>
-          <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AL44" s="17">
-        <v>560</v>
-      </c>
-      <c r="AM44" s="11" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK44" s="11"/>
+      <c r="AL44" s="17"/>
+      <c r="AM44" s="11"/>
       <c r="AN44" s="11"/>
       <c r="AO44" s="11"/>
       <c r="AP44"/>
-      <c r="AQ44" s="17">
-        <v>10</v>
-      </c>
-      <c r="AR44" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS44" s="12" t="inlineStr">
-        <is>
-          <t>Megastar Store</t>
-        </is>
-      </c>
-      <c r="AT44" s="11" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU44" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV44" s="12" t="inlineStr">
-        <is>
-          <t>No.35 Jiuhuan Road, Jiubao Town,</t>
-        </is>
-      </c>
-      <c r="AW44" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES</t>
-        </is>
-      </c>
+      <c r="AQ44" s="17"/>
+      <c r="AR44" s="17"/>
+      <c r="AS44" s="12"/>
+      <c r="AT44" s="11"/>
+      <c r="AU44" s="11"/>
+      <c r="AV44" s="12"/>
+      <c r="AW44" s="11"/>
       <c r="AX44" s="11"/>
-      <c r="AY44" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY44" s="11"/>
       <c r="AZ44" s="11"/>
       <c r="BA44" s="11"/>
       <c r="BB44" s="11"/>
-      <c r="BC44" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD44" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC44" s="11"/>
+      <c r="BD44" s="11"/>
       <c r="BE44" s="11"/>
       <c r="BF44" s="11"/>
       <c r="BG44" s="11"/>
       <c r="BH44" s="12"/>
-      <c r="BI44" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
-      <c r="BJ44" s="20" t="inlineStr">
-        <is>
-          <t>2.28 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK44" s="20" t="inlineStr">
-        <is>
-          <t>2.28 kg</t>
-        </is>
-      </c>
-      <c r="BL44" s="20" t="inlineStr">
-        <is>
-          <t>32.3 x 23.9 x 16.3 cm</t>
-        </is>
-      </c>
-      <c r="BM44" s="20" t="inlineStr">
-        <is>
-          <t>32.30 x 23.90 x 16.30 cm</t>
-        </is>
-      </c>
-      <c r="BN44" s="20" t="inlineStr">
-        <is>
-          <t>2.28 kg</t>
-        </is>
-      </c>
-      <c r="BO44" s="20" t="inlineStr">
-        <is>
-          <t>2.28 kg</t>
-        </is>
-      </c>
-      <c r="BP44" s="20" t="inlineStr">
-        <is>
-          <t>32.3 x 23.9 x 16.3 cm</t>
-        </is>
-      </c>
-      <c r="BQ44" s="20" t="inlineStr">
-        <is>
-          <t>32.30 x 23.90 x 16.30 cm</t>
-        </is>
-      </c>
-      <c r="BR44" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
+      <c r="BI44" s="20"/>
+      <c r="BJ44" s="20"/>
+      <c r="BK44" s="20"/>
+      <c r="BL44" s="20"/>
+      <c r="BM44" s="20"/>
+      <c r="BN44" s="20"/>
+      <c r="BO44" s="20"/>
+      <c r="BP44" s="20"/>
+      <c r="BQ44" s="20"/>
+      <c r="BR44" s="11"/>
     </row>
     <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
@@ -16966,155 +16456,83 @@
       <c r="B45" s="11"/>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>B0HHM96S2L</t>
+          <t>B0DC9P3BH4</t>
         </is>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="12"/>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>udodik</t>
-        </is>
-      </c>
+      <c r="F45" s="12"/>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/udodik/b/ref=bl_dp_s_web_21106953051?ie=UTF8&amp;node=21106953051&amp;field-lbr_brands_browse-bin=udodik</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>Udodik 蒸汽清洁器是一款家用便携式蒸汽清洁器,配有 10 件配件套装,可用于各种表面,天然材料,不含化学物。家庭、厨房、汽车、地毯、年终清洁等。</t>
+          <t>Hapyvergo 蒸汽清洁器 轻松去除污垢 高温蒸汽清洗机 可用于洗涤剂阀 1600W强力操作 20S 速热 105℃高温除菌 日语说明书s清洁刷头替换简单操作大容量水箱家用高温蒸汽清洗机厨房/抽油烟机/马桶清洁轻巧便携尺寸</t>
         </is>
       </c>
       <c r="I45" s="12"/>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HHM96S2L?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DC9P3BH4?psc=1</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41C7wf1aFFL._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/71pzrJ+pdoL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>B0HHM96S2L</t>
-        </is>
-      </c>
-      <c r="M45" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン:家電:生活家電:スチームクリーナー</t>
-        </is>
-      </c>
-      <c r="N45" s="12" t="inlineStr">
-        <is>
-          <t>ホーム＆キッチン</t>
-        </is>
-      </c>
-      <c r="O45" s="13">
-        <v>57570</v>
-      </c>
-      <c r="P45" s="13">
-        <v>116268</v>
-      </c>
-      <c r="Q45" s="14">
-        <v>0.67</v>
-      </c>
-      <c r="R45" s="15" t="inlineStr">
-        <is>
-          <t>スチームクリーナー</t>
-        </is>
-      </c>
-      <c r="S45" s="16" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="T45" s="13">
-        <v>14</v>
-      </c>
+          <t>B0DC9P3BH4</t>
+        </is>
+      </c>
+      <c r="M45" s="12"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="13"/>
+      <c r="P45" s="13"/>
+      <c r="Q45" s="14"/>
+      <c r="R45" s="15"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="13"/>
       <c r="U45" s="14"/>
-      <c r="V45" s="13">
-        <v>93086</v>
-      </c>
+      <c r="V45" s="13"/>
       <c r="W45" s="13"/>
       <c r="X45" s="13"/>
-      <c r="Y45" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="13">
-        <v>6649</v>
-      </c>
+      <c r="Y45" s="17"/>
+      <c r="Z45" s="13"/>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="17">
-        <v>3</v>
-      </c>
-      <c r="AE45" s="13">
-        <v>2</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="AE45" s="13"/>
       <c r="AF45" s="18">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AG45" s="19">
-        <v>0.1429</v>
-      </c>
-      <c r="AH45" s="13">
-        <v>472</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH45" s="13"/>
       <c r="AI45" s="14">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="AJ45"/>
-      <c r="AK45" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AL45" s="17">
-        <v>34</v>
-      </c>
-      <c r="AM45" s="11" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK45" s="11"/>
+      <c r="AL45" s="17"/>
+      <c r="AM45" s="11"/>
       <c r="AN45" s="11"/>
       <c r="AO45" s="11"/>
       <c r="AP45"/>
-      <c r="AQ45" s="17">
-        <v>6</v>
-      </c>
-      <c r="AR45" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS45" s="12" t="inlineStr">
-        <is>
-          <t>jinanrenxianchengxinxikejiyouxiangongsi</t>
-        </is>
-      </c>
-      <c r="AT45" s="11" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU45" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV45" s="12" t="inlineStr">
-        <is>
-          <t>济南市 山东 250100 CN</t>
-        </is>
-      </c>
-      <c r="AW45" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3LLGXOKFXGBZY</t>
-        </is>
-      </c>
+      <c r="AQ45" s="17"/>
+      <c r="AR45" s="17"/>
+      <c r="AS45" s="12"/>
+      <c r="AT45" s="11"/>
+      <c r="AU45" s="11"/>
+      <c r="AV45" s="12"/>
+      <c r="AW45" s="11"/>
       <c r="AX45" s="11"/>
       <c r="AY45" s="11"/>
       <c r="AZ45" s="11"/>
@@ -17127,43 +16545,15 @@
       <c r="BG45" s="11"/>
       <c r="BH45" s="12"/>
       <c r="BI45" s="20"/>
-      <c r="BJ45" s="20" t="inlineStr">
-        <is>
-          <t>2.08 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK45" s="20" t="inlineStr">
-        <is>
-          <t>2.08 kg</t>
-        </is>
-      </c>
+      <c r="BJ45" s="20"/>
+      <c r="BK45" s="20"/>
       <c r="BL45" s="20"/>
       <c r="BM45" s="20"/>
-      <c r="BN45" s="20" t="inlineStr">
-        <is>
-          <t>2.08 kg</t>
-        </is>
-      </c>
-      <c r="BO45" s="20" t="inlineStr">
-        <is>
-          <t>2.08 kg</t>
-        </is>
-      </c>
-      <c r="BP45" s="20" t="inlineStr">
-        <is>
-          <t>27.3 x 26.5 x 20 cm</t>
-        </is>
-      </c>
-      <c r="BQ45" s="20" t="inlineStr">
-        <is>
-          <t>27.30 x 26.50 x 20.00 cm</t>
-        </is>
-      </c>
-      <c r="BR45" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN45" s="20"/>
+      <c r="BO45" s="20"/>
+      <c r="BP45" s="20"/>
+      <c r="BQ45" s="20"/>
+      <c r="BR45" s="11"/>
     </row>
     <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
@@ -17172,7 +16562,7 @@
       <c r="B46" s="11"/>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>B0151FQ7PU</t>
+          <t>B0FL17N46W</t>
         </is>
       </c>
       <c r="D46" s="12"/>
@@ -17185,23 +16575,23 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>H2O 蒸汽FX 8件豪华套装 (绿色)</t>
+          <t>【100℃高温蒸汽×16000Pa超强吸力】SOLEMOOD 地毯清洁剂 家用蒸汽清洁剂 漂浮污垢强力吸力 地毯清洗机 布清洗机 沙发清洁剂 带去污功能 沙发/地毯毯/床垫/车内/玩偶/宠物座椅适用 (灰色)</t>
         </is>
       </c>
       <c r="I46" s="12"/>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0151FQ7PU?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FL17N46W?psc=1</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61LMfetbCwL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/614fPWqO3uL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
-          <t>B0151FQ7PU</t>
+          <t>B0FL17N46W</t>
         </is>
       </c>
       <c r="M46" s="12"/>
@@ -17221,13 +16611,9 @@
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="2"/>
-      <c r="AD46" s="17">
-        <v>423</v>
-      </c>
+      <c r="AD46" s="17"/>
       <c r="AE46" s="13"/>
-      <c r="AF46" s="18">
-        <v>3</v>
-      </c>
+      <c r="AF46" s="18"/>
       <c r="AG46" s="19">
         <v>0</v>
       </c>
@@ -17278,7 +16664,7 @@
       <c r="B47" s="11"/>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>B09JJLTTX3</t>
+          <t>B0FPWXHGQK</t>
         </is>
       </c>
       <c r="D47" s="12"/>
@@ -17291,23 +16677,23 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>ケルヒャー(KARCHER) 蒸汽拖把 SC Upright 1.513-349.0</t>
+          <t>海尔 水洗吸尘器 吸力15000Pa 加热式 蒸汽式 大容量水箱 自动喷水 小巧 带刷子 白色 JC-RPS1A</t>
         </is>
       </c>
       <c r="I47" s="12"/>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B09JJLTTX3?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FPWXHGQK?psc=1</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41s1gdhaMXL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61ojBNldYaL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>B09JJLTTX3</t>
+          <t>B0FPWXHGQK</t>
         </is>
       </c>
       <c r="M47" s="12"/>
@@ -17323,16 +16709,18 @@
       <c r="W47" s="13"/>
       <c r="X47" s="13"/>
       <c r="Y47" s="17"/>
-      <c r="Z47" s="13"/>
+      <c r="Z47" s="13">
+        <v>136</v>
+      </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="17">
-        <v>211</v>
+        <v>12</v>
       </c>
       <c r="AE47" s="13"/>
       <c r="AF47" s="18">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AG47" s="19">
         <v>0</v>
@@ -17376,430 +16764,6 @@
       <c r="BP47" s="20"/>
       <c r="BQ47" s="20"/>
       <c r="BR47" s="11"/>
-    </row>
-    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="11">
-        <v>47</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>B0CZ3TPQLS</t>
-        </is>
-      </c>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>【24年新发布】 凯希（Karcher）蒸汽清洁器 SC2 EasyFix W 标准型 高温稳定蒸汽锅炉加热 浮起顽固污渍 仅用水消毒除臭 地板清洁 油污 地毯 干爽地板 水垢 厨房 浴室 玄关 厕所 车辆 衣物 配件齐全 选配配件丰富 1.512-</t>
-        </is>
-      </c>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0CZ3TPQLS?psc=1</t>
-        </is>
-      </c>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51f3q63b8bL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr">
-        <is>
-          <t>B0CZ3TPQLS</t>
-        </is>
-      </c>
-      <c r="M48" s="12"/>
-      <c r="N48" s="12"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13"/>
-      <c r="Q48" s="14"/>
-      <c r="R48" s="15"/>
-      <c r="S48" s="16"/>
-      <c r="T48" s="13"/>
-      <c r="U48" s="14"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="13"/>
-      <c r="X48" s="13"/>
-      <c r="Y48" s="17"/>
-      <c r="Z48" s="13">
-        <v>147</v>
-      </c>
-      <c r="AA48"/>
-      <c r="AB48"/>
-      <c r="AC48" s="2"/>
-      <c r="AD48" s="17">
-        <v>59</v>
-      </c>
-      <c r="AE48" s="13"/>
-      <c r="AF48" s="18">
-        <v>4</v>
-      </c>
-      <c r="AG48" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="13"/>
-      <c r="AI48" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ48"/>
-      <c r="AK48" s="11"/>
-      <c r="AL48" s="17"/>
-      <c r="AM48" s="11"/>
-      <c r="AN48" s="11"/>
-      <c r="AO48" s="11"/>
-      <c r="AP48"/>
-      <c r="AQ48" s="17"/>
-      <c r="AR48" s="17"/>
-      <c r="AS48" s="12"/>
-      <c r="AT48" s="11"/>
-      <c r="AU48" s="11"/>
-      <c r="AV48" s="12"/>
-      <c r="AW48" s="11"/>
-      <c r="AX48" s="11"/>
-      <c r="AY48" s="11"/>
-      <c r="AZ48" s="11"/>
-      <c r="BA48" s="11"/>
-      <c r="BB48" s="11"/>
-      <c r="BC48" s="11"/>
-      <c r="BD48" s="11"/>
-      <c r="BE48" s="11"/>
-      <c r="BF48" s="11"/>
-      <c r="BG48" s="11"/>
-      <c r="BH48" s="12"/>
-      <c r="BI48" s="20"/>
-      <c r="BJ48" s="20"/>
-      <c r="BK48" s="20"/>
-      <c r="BL48" s="20"/>
-      <c r="BM48" s="20"/>
-      <c r="BN48" s="20"/>
-      <c r="BO48" s="20"/>
-      <c r="BP48" s="20"/>
-      <c r="BQ48" s="20"/>
-      <c r="BR48" s="11"/>
-    </row>
-    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="11">
-        <v>48</v>
-      </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>B0DC9P3BH4</t>
-        </is>
-      </c>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>Hapyvergo 蒸汽清洁器 轻松去除污垢 高温蒸汽清洗机 可用于洗涤剂阀 1600W强力操作 20S 速热 105℃高温除菌 日语说明书s清洁刷头替换简单操作大容量水箱家用高温蒸汽清洗机厨房/抽油烟机/马桶清洁轻巧便携尺寸</t>
-        </is>
-      </c>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0DC9P3BH4?psc=1</t>
-        </is>
-      </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/71pzrJ+pdoL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
-        <is>
-          <t>B0DC9P3BH4</t>
-        </is>
-      </c>
-      <c r="M49" s="12"/>
-      <c r="N49" s="12"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="14"/>
-      <c r="R49" s="15"/>
-      <c r="S49" s="16"/>
-      <c r="T49" s="13"/>
-      <c r="U49" s="14"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="17"/>
-      <c r="Z49" s="13"/>
-      <c r="AA49"/>
-      <c r="AB49"/>
-      <c r="AC49" s="2"/>
-      <c r="AD49" s="17">
-        <v>15</v>
-      </c>
-      <c r="AE49" s="13"/>
-      <c r="AF49" s="18">
-        <v>3.4</v>
-      </c>
-      <c r="AG49" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="13"/>
-      <c r="AI49" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ49"/>
-      <c r="AK49" s="11"/>
-      <c r="AL49" s="17"/>
-      <c r="AM49" s="11"/>
-      <c r="AN49" s="11"/>
-      <c r="AO49" s="11"/>
-      <c r="AP49"/>
-      <c r="AQ49" s="17"/>
-      <c r="AR49" s="17"/>
-      <c r="AS49" s="12"/>
-      <c r="AT49" s="11"/>
-      <c r="AU49" s="11"/>
-      <c r="AV49" s="12"/>
-      <c r="AW49" s="11"/>
-      <c r="AX49" s="11"/>
-      <c r="AY49" s="11"/>
-      <c r="AZ49" s="11"/>
-      <c r="BA49" s="11"/>
-      <c r="BB49" s="11"/>
-      <c r="BC49" s="11"/>
-      <c r="BD49" s="11"/>
-      <c r="BE49" s="11"/>
-      <c r="BF49" s="11"/>
-      <c r="BG49" s="11"/>
-      <c r="BH49" s="12"/>
-      <c r="BI49" s="20"/>
-      <c r="BJ49" s="20"/>
-      <c r="BK49" s="20"/>
-      <c r="BL49" s="20"/>
-      <c r="BM49" s="20"/>
-      <c r="BN49" s="20"/>
-      <c r="BO49" s="20"/>
-      <c r="BP49" s="20"/>
-      <c r="BQ49" s="20"/>
-      <c r="BR49" s="11"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="11">
-        <v>49</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>B0FL17N46W</t>
-        </is>
-      </c>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>【100℃高温蒸汽×16000Pa超强吸力】SOLEMOOD 地毯清洁剂 家用蒸汽清洁剂 漂浮污垢强力吸力 地毯清洗机 布清洗机 沙发清洁剂 带去污功能 沙发/地毯毯/床垫/车内/玩偶/宠物座椅适用 (灰色)</t>
-        </is>
-      </c>
-      <c r="I50" s="12"/>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0FL17N46W?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/614fPWqO3uL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>B0FL17N46W</t>
-        </is>
-      </c>
-      <c r="M50" s="12"/>
-      <c r="N50" s="12"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="13"/>
-      <c r="Q50" s="14"/>
-      <c r="R50" s="15"/>
-      <c r="S50" s="16"/>
-      <c r="T50" s="13"/>
-      <c r="U50" s="14"/>
-      <c r="V50" s="13"/>
-      <c r="W50" s="13"/>
-      <c r="X50" s="13"/>
-      <c r="Y50" s="17"/>
-      <c r="Z50" s="13"/>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="17"/>
-      <c r="AE50" s="13"/>
-      <c r="AF50" s="18"/>
-      <c r="AG50" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="13"/>
-      <c r="AI50" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="11"/>
-      <c r="AL50" s="17"/>
-      <c r="AM50" s="11"/>
-      <c r="AN50" s="11"/>
-      <c r="AO50" s="11"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="17"/>
-      <c r="AR50" s="17"/>
-      <c r="AS50" s="12"/>
-      <c r="AT50" s="11"/>
-      <c r="AU50" s="11"/>
-      <c r="AV50" s="12"/>
-      <c r="AW50" s="11"/>
-      <c r="AX50" s="11"/>
-      <c r="AY50" s="11"/>
-      <c r="AZ50" s="11"/>
-      <c r="BA50" s="11"/>
-      <c r="BB50" s="11"/>
-      <c r="BC50" s="11"/>
-      <c r="BD50" s="11"/>
-      <c r="BE50" s="11"/>
-      <c r="BF50" s="11"/>
-      <c r="BG50" s="11"/>
-      <c r="BH50" s="12"/>
-      <c r="BI50" s="20"/>
-      <c r="BJ50" s="20"/>
-      <c r="BK50" s="20"/>
-      <c r="BL50" s="20"/>
-      <c r="BM50" s="20"/>
-      <c r="BN50" s="20"/>
-      <c r="BO50" s="20"/>
-      <c r="BP50" s="20"/>
-      <c r="BQ50" s="20"/>
-      <c r="BR50" s="11"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
-        <v>50</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>B0FPWXHGQK</t>
-        </is>
-      </c>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>海尔 水洗吸尘器 吸力15000Pa 加热式 蒸汽式 大容量水箱 自动喷水 小巧 带刷子 白色 JC-RPS1A</t>
-        </is>
-      </c>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0FPWXHGQK?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61ojBNldYaL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>B0FPWXHGQK</t>
-        </is>
-      </c>
-      <c r="M51" s="12"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="14"/>
-      <c r="R51" s="15"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="13"/>
-      <c r="U51" s="14"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="17"/>
-      <c r="Z51" s="13">
-        <v>136</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="17">
-        <v>12</v>
-      </c>
-      <c r="AE51" s="13"/>
-      <c r="AF51" s="18">
-        <v>3.8</v>
-      </c>
-      <c r="AG51" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="13"/>
-      <c r="AI51" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="11"/>
-      <c r="AL51" s="17"/>
-      <c r="AM51" s="11"/>
-      <c r="AN51" s="11"/>
-      <c r="AO51" s="11"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="17"/>
-      <c r="AR51" s="17"/>
-      <c r="AS51" s="12"/>
-      <c r="AT51" s="11"/>
-      <c r="AU51" s="11"/>
-      <c r="AV51" s="12"/>
-      <c r="AW51" s="11"/>
-      <c r="AX51" s="11"/>
-      <c r="AY51" s="11"/>
-      <c r="AZ51" s="11"/>
-      <c r="BA51" s="11"/>
-      <c r="BB51" s="11"/>
-      <c r="BC51" s="11"/>
-      <c r="BD51" s="11"/>
-      <c r="BE51" s="11"/>
-      <c r="BF51" s="11"/>
-      <c r="BG51" s="11"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51" s="20"/>
-      <c r="BJ51" s="20"/>
-      <c r="BK51" s="20"/>
-      <c r="BL51" s="20"/>
-      <c r="BM51" s="20"/>
-      <c r="BN51" s="20"/>
-      <c r="BO51" s="20"/>
-      <c r="BP51" s="20"/>
-      <c r="BQ51" s="20"/>
-      <c r="BR51" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17980,220 +16944,188 @@
     <hyperlink ref="M23" r:id="rId173" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N23" r:id="rId174"/>
     <hyperlink ref="AW23" r:id="rId175" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2L4LHXL144SJ"/>
-    <hyperlink ref="C24" r:id="rId176" tooltip="https://www.amazon.co.jp/dp/B0H7B99X6W"/>
-    <hyperlink ref="G24" r:id="rId177" tooltip="https://www.amazon.co.jp/stores/%E3%83%97%E3%83%A9%E3%82%B9%E3%83%9E%E3%82%A4%E3%83%8A%E3%82%B9%E3%82%BC%E3%83%AD/page/F8BCEE33-4642-4879-8043-6C340A3D69AB?lp_asin=B0H7B99X6W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J24" r:id="rId178" tooltip="https://www.amazon.co.jp/dp/B0H7B99X6W?psc=1"/>
-    <hyperlink ref="K24" r:id="rId179" tooltip="https://m.media-amazon.com/images/I/51C5hYWM0yL._AC_US600_.jpg"/>
-    <hyperlink ref="L24" r:id="rId180" tooltip="https://www.amazon.co.jp/dp/B0H7B99X6W"/>
+    <hyperlink ref="C24" r:id="rId176" tooltip="https://www.amazon.co.jp/dp/B0FWCRWS4J"/>
+    <hyperlink ref="G24" r:id="rId177" tooltip="https://www.amazon.co.jp/stores/YINOLIFE/page/B4E9A7F4-5909-4351-B434-6EF367427B37?lp_asin=B0FWCRWS4J&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J24" r:id="rId178" tooltip="https://www.amazon.co.jp/dp/B0FWCRWS4J?psc=1"/>
+    <hyperlink ref="K24" r:id="rId179" tooltip="https://m.media-amazon.com/images/I/41aG6lp2gKL._AC_US600_.jpg"/>
+    <hyperlink ref="L24" r:id="rId180" tooltip="https://www.amazon.co.jp/dp/B0FWCRWS4J"/>
     <hyperlink ref="M24" r:id="rId181" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N24" r:id="rId182"/>
-    <hyperlink ref="AW24" r:id="rId183" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SVARFDL9L32I"/>
-    <hyperlink ref="C25" r:id="rId184" tooltip="https://www.amazon.co.jp/dp/B0FWCRWS4J"/>
-    <hyperlink ref="G25" r:id="rId185" tooltip="https://www.amazon.co.jp/stores/YINOLIFE/page/B4E9A7F4-5909-4351-B434-6EF367427B37?lp_asin=B0FWCRWS4J&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J25" r:id="rId186" tooltip="https://www.amazon.co.jp/dp/B0FWCRWS4J?psc=1"/>
-    <hyperlink ref="K25" r:id="rId187" tooltip="https://m.media-amazon.com/images/I/41aG6lp2gKL._AC_US600_.jpg"/>
-    <hyperlink ref="L25" r:id="rId188" tooltip="https://www.amazon.co.jp/dp/B0FWCRWS4J"/>
+    <hyperlink ref="AW24" r:id="rId183" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3BEVRYR6RB3FY"/>
+    <hyperlink ref="C25" r:id="rId184" tooltip="https://www.amazon.co.jp/dp/B0H1LV9Z1W"/>
+    <hyperlink ref="G25" r:id="rId185" tooltip="https://www.amazon.co.jp/udodik/b/ref=bl_dp_s_web_21106953051?ie=UTF8&amp;node=21106953051&amp;field-lbr_brands_browse-bin=udodik"/>
+    <hyperlink ref="J25" r:id="rId186" tooltip="https://www.amazon.co.jp/dp/B0H1LV9Z1W?psc=1"/>
+    <hyperlink ref="K25" r:id="rId187" tooltip="https://m.media-amazon.com/images/I/41hNJ+tmXEL._AC_US600_.jpg"/>
+    <hyperlink ref="L25" r:id="rId188" tooltip="https://www.amazon.co.jp/dp/B0H1LV9Z1W"/>
     <hyperlink ref="M25" r:id="rId189" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N25" r:id="rId190"/>
-    <hyperlink ref="AW25" r:id="rId191" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3BEVRYR6RB3FY"/>
-    <hyperlink ref="C26" r:id="rId192" tooltip="https://www.amazon.co.jp/dp/B0H1LV9Z1W"/>
-    <hyperlink ref="G26" r:id="rId193" tooltip="https://www.amazon.co.jp/udodik/b/ref=bl_dp_s_web_21106953051?ie=UTF8&amp;node=21106953051&amp;field-lbr_brands_browse-bin=udodik"/>
-    <hyperlink ref="J26" r:id="rId194" tooltip="https://www.amazon.co.jp/dp/B0H1LV9Z1W?psc=1"/>
-    <hyperlink ref="K26" r:id="rId195" tooltip="https://m.media-amazon.com/images/I/41hNJ+tmXEL._AC_US600_.jpg"/>
-    <hyperlink ref="L26" r:id="rId196" tooltip="https://www.amazon.co.jp/dp/B0H1LV9Z1W"/>
+    <hyperlink ref="AW25" r:id="rId191" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3LLGXOKFXGBZY"/>
+    <hyperlink ref="C26" r:id="rId192" tooltip="https://www.amazon.co.jp/dp/B0BLHZDTDP"/>
+    <hyperlink ref="G26" r:id="rId193" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0BLHZDTDP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J26" r:id="rId194" tooltip="https://www.amazon.co.jp/dp/B0BLHZDTDP?psc=1"/>
+    <hyperlink ref="K26" r:id="rId195" tooltip="https://m.media-amazon.com/images/I/41B2GvpD-eL._AC_US600_.jpg"/>
+    <hyperlink ref="L26" r:id="rId196" tooltip="https://www.amazon.co.jp/dp/B0BLHZDTDP"/>
     <hyperlink ref="M26" r:id="rId197" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N26" r:id="rId198"/>
-    <hyperlink ref="AW26" r:id="rId199" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3LLGXOKFXGBZY"/>
-    <hyperlink ref="C27" r:id="rId200" tooltip="https://www.amazon.co.jp/dp/B0BLHZDTDP"/>
-    <hyperlink ref="G27" r:id="rId201" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0BLHZDTDP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J27" r:id="rId202" tooltip="https://www.amazon.co.jp/dp/B0BLHZDTDP?psc=1"/>
-    <hyperlink ref="K27" r:id="rId203" tooltip="https://m.media-amazon.com/images/I/41B2GvpD-eL._AC_US600_.jpg"/>
-    <hyperlink ref="L27" r:id="rId204" tooltip="https://www.amazon.co.jp/dp/B0BLHZDTDP"/>
+    <hyperlink ref="AW26" r:id="rId199" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A16H9JXI44PW5O"/>
+    <hyperlink ref="C27" r:id="rId200" tooltip="https://www.amazon.co.jp/dp/B0GHMZNCVL"/>
+    <hyperlink ref="G27" r:id="rId201" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Karcher"/>
+    <hyperlink ref="J27" r:id="rId202" tooltip="https://www.amazon.co.jp/dp/B0GHMZNCVL?psc=1"/>
+    <hyperlink ref="K27" r:id="rId203" tooltip="https://m.media-amazon.com/images/I/41eNQ9I14nL._AC_US600_.jpg"/>
+    <hyperlink ref="L27" r:id="rId204" tooltip="https://www.amazon.co.jp/dp/B0GHMZNCVL"/>
     <hyperlink ref="M27" r:id="rId205" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N27" r:id="rId206"/>
-    <hyperlink ref="AW27" r:id="rId207" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A16H9JXI44PW5O"/>
-    <hyperlink ref="C28" r:id="rId208" tooltip="https://www.amazon.co.jp/dp/B0GHMZNCVL"/>
-    <hyperlink ref="G28" r:id="rId209" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=Karcher"/>
-    <hyperlink ref="J28" r:id="rId210" tooltip="https://www.amazon.co.jp/dp/B0GHMZNCVL?psc=1"/>
-    <hyperlink ref="K28" r:id="rId211" tooltip="https://m.media-amazon.com/images/I/41eNQ9I14nL._AC_US600_.jpg"/>
-    <hyperlink ref="L28" r:id="rId212" tooltip="https://www.amazon.co.jp/dp/B0GHMZNCVL"/>
+    <hyperlink ref="AW27" r:id="rId207" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZHWG2831WCH8"/>
+    <hyperlink ref="C28" r:id="rId208" tooltip="https://www.amazon.co.jp/dp/B07GXPG63H"/>
+    <hyperlink ref="G28" r:id="rId209" tooltip="https://www.amazon.co.jp/stores/%E3%82%B1%E3%83%AB%E3%83%92%E3%83%A3%E3%83%BCKARCHER/page/C3335239-5EF7-43A7-B432-CEBBBE4E3C9B?lp_asin=B07GXPG63H&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J28" r:id="rId210" tooltip="https://www.amazon.co.jp/dp/B07GXPG63H?psc=1"/>
+    <hyperlink ref="K28" r:id="rId211" tooltip="https://m.media-amazon.com/images/I/41H+7reLbSL._AC_US600_.jpg"/>
+    <hyperlink ref="L28" r:id="rId212" tooltip="https://www.amazon.co.jp/dp/B07GXPG63H"/>
     <hyperlink ref="M28" r:id="rId213" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N28" r:id="rId214"/>
-    <hyperlink ref="AW28" r:id="rId215" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZHWG2831WCH8"/>
-    <hyperlink ref="C29" r:id="rId216" tooltip="https://www.amazon.co.jp/dp/B07GXPG63H"/>
-    <hyperlink ref="G29" r:id="rId217" tooltip="https://www.amazon.co.jp/stores/%E3%82%B1%E3%83%AB%E3%83%92%E3%83%A3%E3%83%BCKARCHER/page/C3335239-5EF7-43A7-B432-CEBBBE4E3C9B?lp_asin=B07GXPG63H&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J29" r:id="rId218" tooltip="https://www.amazon.co.jp/dp/B07GXPG63H?psc=1"/>
-    <hyperlink ref="K29" r:id="rId219" tooltip="https://m.media-amazon.com/images/I/41H+7reLbSL._AC_US600_.jpg"/>
-    <hyperlink ref="L29" r:id="rId220" tooltip="https://www.amazon.co.jp/dp/B07GXPG63H"/>
+    <hyperlink ref="AW28" r:id="rId215" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WEN0WQL6IM1B"/>
+    <hyperlink ref="C29" r:id="rId216" tooltip="https://www.amazon.co.jp/dp/B0C6F9FBV1"/>
+    <hyperlink ref="G29" r:id="rId217" tooltip="https://www.amazon.co.jp/stores/Mistsince/page/D3BF9035-65AB-4860-9B3C-F101376ACA73?lp_asin=B0C6F9FBV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J29" r:id="rId218" tooltip="https://www.amazon.co.jp/dp/B0C6F9FBV1?psc=1"/>
+    <hyperlink ref="K29" r:id="rId219" tooltip="https://m.media-amazon.com/images/I/31Z+dPKeqqL._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId220" tooltip="https://www.amazon.co.jp/dp/B0C6F9FBV1"/>
     <hyperlink ref="M29" r:id="rId221" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N29" r:id="rId222"/>
-    <hyperlink ref="AW29" r:id="rId223" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WEN0WQL6IM1B"/>
-    <hyperlink ref="C30" r:id="rId224" tooltip="https://www.amazon.co.jp/dp/B0C6F9FBV1"/>
-    <hyperlink ref="G30" r:id="rId225" tooltip="https://www.amazon.co.jp/stores/Mistsince/page/D3BF9035-65AB-4860-9B3C-F101376ACA73?lp_asin=B0C6F9FBV1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J30" r:id="rId226" tooltip="https://www.amazon.co.jp/dp/B0C6F9FBV1?psc=1"/>
-    <hyperlink ref="K30" r:id="rId227" tooltip="https://m.media-amazon.com/images/I/31Z+dPKeqqL._AC_US600_.jpg"/>
-    <hyperlink ref="L30" r:id="rId228" tooltip="https://www.amazon.co.jp/dp/B0C6F9FBV1"/>
+    <hyperlink ref="AW29" r:id="rId223" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AVZ7LMXDP1WK4"/>
+    <hyperlink ref="C30" r:id="rId224" tooltip="https://www.amazon.co.jp/dp/B0CLYBB2QG"/>
+    <hyperlink ref="G30" r:id="rId225" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0CLYBB2QG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J30" r:id="rId226" tooltip="https://www.amazon.co.jp/dp/B0CLYBB2QG?psc=1"/>
+    <hyperlink ref="K30" r:id="rId227" tooltip="https://m.media-amazon.com/images/I/31eHl3QohpL._AC_US600_.jpg"/>
+    <hyperlink ref="L30" r:id="rId228" tooltip="https://www.amazon.co.jp/dp/B0CLYBB2QG"/>
     <hyperlink ref="M30" r:id="rId229" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N30" r:id="rId230"/>
-    <hyperlink ref="AW30" r:id="rId231" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AVZ7LMXDP1WK4"/>
-    <hyperlink ref="C31" r:id="rId232" tooltip="https://www.amazon.co.jp/dp/B0CLYBB2QG"/>
-    <hyperlink ref="G31" r:id="rId233" tooltip="https://www.amazon.co.jp/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0CLYBB2QG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J31" r:id="rId234" tooltip="https://www.amazon.co.jp/dp/B0CLYBB2QG?psc=1"/>
-    <hyperlink ref="K31" r:id="rId235" tooltip="https://m.media-amazon.com/images/I/31eHl3QohpL._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId236" tooltip="https://www.amazon.co.jp/dp/B0CLYBB2QG"/>
+    <hyperlink ref="AW30" r:id="rId231" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WPB6AY1N585H"/>
+    <hyperlink ref="C31" r:id="rId232" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN"/>
+    <hyperlink ref="G31" r:id="rId233" tooltip="https://www.amazon.co.jp/stores/Waitbird/page/3EF06D38-11FF-4AB3-B913-B77B78E9E2C6?lp_asin=B0HK3489BN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J31" r:id="rId234" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN?psc=1"/>
+    <hyperlink ref="K31" r:id="rId235" tooltip="https://m.media-amazon.com/images/I/41uxuzLFDeL._AC_US600_.jpg"/>
+    <hyperlink ref="L31" r:id="rId236" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN"/>
     <hyperlink ref="M31" r:id="rId237" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N31" r:id="rId238"/>
-    <hyperlink ref="AW31" r:id="rId239" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WPB6AY1N585H"/>
-    <hyperlink ref="C32" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN"/>
-    <hyperlink ref="G32" r:id="rId241" tooltip="https://www.amazon.co.jp/stores/Waitbird/page/3EF06D38-11FF-4AB3-B913-B77B78E9E2C6?lp_asin=B0HK3489BN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J32" r:id="rId242" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN?psc=1"/>
-    <hyperlink ref="K32" r:id="rId243" tooltip="https://m.media-amazon.com/images/I/41uxuzLFDeL._AC_US600_.jpg"/>
-    <hyperlink ref="L32" r:id="rId244" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN"/>
+    <hyperlink ref="AW31" r:id="rId239" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3AAS2L1ZEPTML"/>
+    <hyperlink ref="C32" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0GGY1Y4CK"/>
+    <hyperlink ref="G32" r:id="rId241" tooltip="https://www.amazon.co.jp/stores/TOKAIZ/page/9CAE01F0-2A50-4674-BB57-A53225F3A5EA?lp_asin=B0GGY1Y4CK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J32" r:id="rId242" tooltip="https://www.amazon.co.jp/dp/B0GGY1Y4CK?psc=1"/>
+    <hyperlink ref="K32" r:id="rId243" tooltip="https://m.media-amazon.com/images/I/413QwzNv1IL._AC_US600_.jpg"/>
+    <hyperlink ref="L32" r:id="rId244" tooltip="https://www.amazon.co.jp/dp/B0GGY1Y4CK"/>
     <hyperlink ref="M32" r:id="rId245" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N32" r:id="rId246"/>
-    <hyperlink ref="AW32" r:id="rId247" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3AAS2L1ZEPTML"/>
-    <hyperlink ref="C33" r:id="rId248" tooltip="https://www.amazon.co.jp/dp/B0GGY1Y4CK"/>
-    <hyperlink ref="G33" r:id="rId249" tooltip="https://www.amazon.co.jp/stores/TOKAIZ/page/9CAE01F0-2A50-4674-BB57-A53225F3A5EA?lp_asin=B0GGY1Y4CK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J33" r:id="rId250" tooltip="https://www.amazon.co.jp/dp/B0GGY1Y4CK?psc=1"/>
-    <hyperlink ref="K33" r:id="rId251" tooltip="https://m.media-amazon.com/images/I/413QwzNv1IL._AC_US600_.jpg"/>
-    <hyperlink ref="L33" r:id="rId252" tooltip="https://www.amazon.co.jp/dp/B0GGY1Y4CK"/>
+    <hyperlink ref="AW32" r:id="rId247" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A249HMDQ0OTKWV"/>
+    <hyperlink ref="C33" r:id="rId248" tooltip="https://www.amazon.co.jp/dp/B0H8SPVHVZ"/>
+    <hyperlink ref="G33" r:id="rId249" tooltip="https://www.amazon.co.jp/stores/%E3%81%8D%E3%82%8C%E3%81%84%E3%81%AE%E6%99%82%E9%96%93%E3%82%92%E3%80%81%E7%A7%81%E3%81%AE%E6%99%82%E9%96%93%E3%81%AB%E3%80%82/page/B441CACF-20A2-4071-9530-2CC8DA3A24B6?lp_asin=B0H8SPVHVZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J33" r:id="rId250" tooltip="https://www.amazon.co.jp/dp/B0H8SPVHVZ?psc=1"/>
+    <hyperlink ref="K33" r:id="rId251" tooltip="https://m.media-amazon.com/images/I/418sjd-uV7L._AC_US600_.jpg"/>
+    <hyperlink ref="L33" r:id="rId252" tooltip="https://www.amazon.co.jp/dp/B0H8SPVHVZ"/>
     <hyperlink ref="M33" r:id="rId253" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N33" r:id="rId254"/>
-    <hyperlink ref="AW33" r:id="rId255" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A249HMDQ0OTKWV"/>
-    <hyperlink ref="C34" r:id="rId256" tooltip="https://www.amazon.co.jp/dp/B0H8SPVHVZ"/>
-    <hyperlink ref="G34" r:id="rId257" tooltip="https://www.amazon.co.jp/stores/%E3%81%8D%E3%82%8C%E3%81%84%E3%81%AE%E6%99%82%E9%96%93%E3%82%92%E3%80%81%E7%A7%81%E3%81%AE%E6%99%82%E9%96%93%E3%81%AB%E3%80%82/page/B441CACF-20A2-4071-9530-2CC8DA3A24B6?lp_asin=B0H8SPVHVZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J34" r:id="rId258" tooltip="https://www.amazon.co.jp/dp/B0H8SPVHVZ?psc=1"/>
-    <hyperlink ref="K34" r:id="rId259" tooltip="https://m.media-amazon.com/images/I/418sjd-uV7L._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId260" tooltip="https://www.amazon.co.jp/dp/B0H8SPVHVZ"/>
+    <hyperlink ref="AW33" r:id="rId255" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3WKMH8N8T04I"/>
+    <hyperlink ref="C34" r:id="rId256" tooltip="https://www.amazon.co.jp/dp/B0GCCPG7M6"/>
+    <hyperlink ref="G34" r:id="rId257" tooltip="https://www.amazon.co.jp/stores/%E3%81%8D%E3%82%8C%E3%81%84%E3%81%AE%E6%99%82%E9%96%93%E3%82%92%E3%80%81%E7%A7%81%E3%81%AE%E6%99%82%E9%96%93%E3%81%AB%E3%80%82/page/B441CACF-20A2-4071-9530-2CC8DA3A24B6?lp_asin=B0GCCPG7M6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J34" r:id="rId258" tooltip="https://www.amazon.co.jp/dp/B0GCCPG7M6?psc=1"/>
+    <hyperlink ref="K34" r:id="rId259" tooltip="https://m.media-amazon.com/images/I/41YsUtHrVDL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId260" tooltip="https://www.amazon.co.jp/dp/B0GCCPG7M6"/>
     <hyperlink ref="M34" r:id="rId261" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N34" r:id="rId262"/>
     <hyperlink ref="AW34" r:id="rId263" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3WKMH8N8T04I"/>
-    <hyperlink ref="C35" r:id="rId264" tooltip="https://www.amazon.co.jp/dp/B0GCCPG7M6"/>
-    <hyperlink ref="G35" r:id="rId265" tooltip="https://www.amazon.co.jp/stores/%E3%81%8D%E3%82%8C%E3%81%84%E3%81%AE%E6%99%82%E9%96%93%E3%82%92%E3%80%81%E7%A7%81%E3%81%AE%E6%99%82%E9%96%93%E3%81%AB%E3%80%82/page/B441CACF-20A2-4071-9530-2CC8DA3A24B6?lp_asin=B0GCCPG7M6&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J35" r:id="rId266" tooltip="https://www.amazon.co.jp/dp/B0GCCPG7M6?psc=1"/>
-    <hyperlink ref="K35" r:id="rId267" tooltip="https://m.media-amazon.com/images/I/41YsUtHrVDL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId268" tooltip="https://www.amazon.co.jp/dp/B0GCCPG7M6"/>
+    <hyperlink ref="C35" r:id="rId264" tooltip="https://www.amazon.co.jp/dp/B0GF8HHWYQ"/>
+    <hyperlink ref="G35" r:id="rId265" tooltip="https://www.amazon.co.jp/stores/Mistsince/page/D3BF9035-65AB-4860-9B3C-F101376ACA73?lp_asin=B0GF8HHWYQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J35" r:id="rId266" tooltip="https://www.amazon.co.jp/dp/B0GF8HHWYQ?psc=1"/>
+    <hyperlink ref="K35" r:id="rId267" tooltip="https://images-na.ssl-images-amazon.com/images/I/61u2zZZEngL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId268" tooltip="https://www.amazon.co.jp/dp/B0GF8HHWYQ"/>
     <hyperlink ref="M35" r:id="rId269" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N35" r:id="rId270"/>
-    <hyperlink ref="AW35" r:id="rId271" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3WKMH8N8T04I"/>
-    <hyperlink ref="C36" r:id="rId272" tooltip="https://www.amazon.co.jp/dp/B0GF8HHWYQ"/>
-    <hyperlink ref="G36" r:id="rId273" tooltip="https://www.amazon.co.jp/stores/Mistsince/page/D3BF9035-65AB-4860-9B3C-F101376ACA73?lp_asin=B0GF8HHWYQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J36" r:id="rId274" tooltip="https://www.amazon.co.jp/dp/B0GF8HHWYQ?psc=1"/>
-    <hyperlink ref="K36" r:id="rId275" tooltip="https://images-na.ssl-images-amazon.com/images/I/61u2zZZEngL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B0GF8HHWYQ"/>
+    <hyperlink ref="AW35" r:id="rId271" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AVZ7LMXDP1WK4"/>
+    <hyperlink ref="C36" r:id="rId272" tooltip="https://www.amazon.co.jp/dp/B0B3XBM5HW"/>
+    <hyperlink ref="G36" r:id="rId273" tooltip="https://www.amazon.co.jp/stores/%E3%82%B1%E3%83%AB%E3%83%92%E3%83%A3%E3%83%BCKARCHER/page/C3335239-5EF7-43A7-B432-CEBBBE4E3C9B?lp_asin=B0B3XBM5HW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J36" r:id="rId274" tooltip="https://www.amazon.co.jp/dp/B0B3XBM5HW?psc=1"/>
+    <hyperlink ref="K36" r:id="rId275" tooltip="https://m.media-amazon.com/images/I/51Sf-O7BUfL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B0B3XBM5HW"/>
     <hyperlink ref="M36" r:id="rId277" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N36" r:id="rId278"/>
-    <hyperlink ref="AW36" r:id="rId279" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AVZ7LMXDP1WK4"/>
-    <hyperlink ref="C37" r:id="rId280" tooltip="https://www.amazon.co.jp/dp/B0B3XBM5HW"/>
-    <hyperlink ref="G37" r:id="rId281" tooltip="https://www.amazon.co.jp/stores/%E3%82%B1%E3%83%AB%E3%83%92%E3%83%A3%E3%83%BCKARCHER/page/C3335239-5EF7-43A7-B432-CEBBBE4E3C9B?lp_asin=B0B3XBM5HW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J37" r:id="rId282" tooltip="https://www.amazon.co.jp/dp/B0B3XBM5HW?psc=1"/>
-    <hyperlink ref="K37" r:id="rId283" tooltip="https://m.media-amazon.com/images/I/51Sf-O7BUfL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId284" tooltip="https://www.amazon.co.jp/dp/B0B3XBM5HW"/>
+    <hyperlink ref="AW36" r:id="rId279" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AWJMS00CHSZRT"/>
+    <hyperlink ref="C37" r:id="rId280" tooltip="https://www.amazon.co.jp/dp/B0FC4YLXC2"/>
+    <hyperlink ref="G37" r:id="rId281" tooltip="https://www.amazon.co.jp/stores/Yoquna/page/506291FF-A2EF-4B20-AEA8-C1DC1422EAEA?lp_asin=B0FC4YLXC2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J37" r:id="rId282" tooltip="https://www.amazon.co.jp/dp/B0FC4YLXC2?psc=1"/>
+    <hyperlink ref="K37" r:id="rId283" tooltip="https://m.media-amazon.com/images/I/41z81OFfyxL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId284" tooltip="https://www.amazon.co.jp/dp/B0FC4YLXC2"/>
     <hyperlink ref="M37" r:id="rId285" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N37" r:id="rId286"/>
-    <hyperlink ref="AW37" r:id="rId287" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AWJMS00CHSZRT"/>
-    <hyperlink ref="C38" r:id="rId288" tooltip="https://www.amazon.co.jp/dp/B0FC4YLXC2"/>
-    <hyperlink ref="G38" r:id="rId289" tooltip="https://www.amazon.co.jp/stores/Yoquna/page/506291FF-A2EF-4B20-AEA8-C1DC1422EAEA?lp_asin=B0FC4YLXC2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J38" r:id="rId290" tooltip="https://www.amazon.co.jp/dp/B0FC4YLXC2?psc=1"/>
-    <hyperlink ref="K38" r:id="rId291" tooltip="https://m.media-amazon.com/images/I/41z81OFfyxL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId292" tooltip="https://www.amazon.co.jp/dp/B0FC4YLXC2"/>
+    <hyperlink ref="AW37" r:id="rId287" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3KBWI6Y9WW9KR"/>
+    <hyperlink ref="C38" r:id="rId288" tooltip="https://www.amazon.co.jp/dp/B0HBNN64GG"/>
+    <hyperlink ref="G38" r:id="rId289" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=PROSTREET"/>
+    <hyperlink ref="J38" r:id="rId290" tooltip="https://www.amazon.co.jp/dp/B0HBNN64GG?psc=1"/>
+    <hyperlink ref="K38" r:id="rId291" tooltip="https://m.media-amazon.com/images/I/412-JGnvDBL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId292" tooltip="https://www.amazon.co.jp/dp/B0HBNN64GG"/>
     <hyperlink ref="M38" r:id="rId293" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N38" r:id="rId294"/>
-    <hyperlink ref="AW38" r:id="rId295" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3KBWI6Y9WW9KR"/>
-    <hyperlink ref="C39" r:id="rId296" tooltip="https://www.amazon.co.jp/dp/B0HBNN64GG"/>
-    <hyperlink ref="G39" r:id="rId297" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=PROSTREET"/>
-    <hyperlink ref="J39" r:id="rId298" tooltip="https://www.amazon.co.jp/dp/B0HBNN64GG?psc=1"/>
-    <hyperlink ref="K39" r:id="rId299" tooltip="https://m.media-amazon.com/images/I/412-JGnvDBL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId300" tooltip="https://www.amazon.co.jp/dp/B0HBNN64GG"/>
+    <hyperlink ref="AW38" r:id="rId295" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YO7910ANGPIW"/>
+    <hyperlink ref="C39" r:id="rId296" tooltip="https://www.amazon.co.jp/dp/B0HC9N8LCH"/>
+    <hyperlink ref="G39" r:id="rId297" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=G-KiKi"/>
+    <hyperlink ref="J39" r:id="rId298" tooltip="https://www.amazon.co.jp/dp/B0HC9N8LCH?psc=1"/>
+    <hyperlink ref="K39" r:id="rId299" tooltip="https://m.media-amazon.com/images/I/51CZtGWw4AL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId300" tooltip="https://www.amazon.co.jp/dp/B0HC9N8LCH"/>
     <hyperlink ref="M39" r:id="rId301" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N39" r:id="rId302"/>
-    <hyperlink ref="AW39" r:id="rId303" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YO7910ANGPIW"/>
-    <hyperlink ref="C40" r:id="rId304" tooltip="https://www.amazon.co.jp/dp/B0HC9N8LCH"/>
-    <hyperlink ref="G40" r:id="rId305" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=G-KiKi"/>
-    <hyperlink ref="J40" r:id="rId306" tooltip="https://www.amazon.co.jp/dp/B0HC9N8LCH?psc=1"/>
-    <hyperlink ref="K40" r:id="rId307" tooltip="https://m.media-amazon.com/images/I/51CZtGWw4AL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId308" tooltip="https://www.amazon.co.jp/dp/B0HC9N8LCH"/>
+    <hyperlink ref="AW39" r:id="rId303" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A15YNDSRCB68XM"/>
+    <hyperlink ref="C40" r:id="rId304" tooltip="https://www.amazon.co.jp/dp/B0HKYTFSJD"/>
+    <hyperlink ref="G40" r:id="rId305" tooltip="https://www.amazon.co.jp/TopDuterpick/b/ref=bl_dp_s_web_8448083051?ie=UTF8&amp;node=8448083051&amp;field-lbr_brands_browse-bin=TopDuterpick"/>
+    <hyperlink ref="J40" r:id="rId306" tooltip="https://www.amazon.co.jp/dp/B0HKYTFSJD?psc=1"/>
+    <hyperlink ref="K40" r:id="rId307" tooltip="https://m.media-amazon.com/images/I/41srV4Bdl3L._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId308" tooltip="https://www.amazon.co.jp/dp/B0HKYTFSJD"/>
     <hyperlink ref="M40" r:id="rId309" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N40" r:id="rId310"/>
-    <hyperlink ref="AW40" r:id="rId311" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A15YNDSRCB68XM"/>
-    <hyperlink ref="C41" r:id="rId312" tooltip="https://www.amazon.co.jp/dp/B0F4KNH1MF"/>
-    <hyperlink ref="G41" r:id="rId313" tooltip="https://www.amazon.co.jp/stores/bumxca%EF%BC%88%E3%83%90%E3%83%A0%E3%82%B9%E3%82%AB%EF%BC%89%E7%9B%B4%E5%96%B6%E5%85%AC%E5%BC%8F%E5%BA%97/page/EB7E5050-7292-4C62-8EA5-D1F993EEFD10?lp_asin=B0F4KNH1MF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J41" r:id="rId314" tooltip="https://www.amazon.co.jp/dp/B0F4KNH1MF?psc=1"/>
-    <hyperlink ref="K41" r:id="rId315" tooltip="https://m.media-amazon.com/images/I/51r9znyHJXL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId316" tooltip="https://www.amazon.co.jp/dp/B0F4KNH1MF"/>
+    <hyperlink ref="AW40" r:id="rId311" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A18CF0AX3KZRVX"/>
+    <hyperlink ref="C41" r:id="rId312" tooltip="https://www.amazon.co.jp/dp/B0HHM96S2L"/>
+    <hyperlink ref="G41" r:id="rId313" tooltip="https://www.amazon.co.jp/udodik/b/ref=bl_dp_s_web_21106953051?ie=UTF8&amp;node=21106953051&amp;field-lbr_brands_browse-bin=udodik"/>
+    <hyperlink ref="J41" r:id="rId314" tooltip="https://www.amazon.co.jp/dp/B0HHM96S2L?psc=1"/>
+    <hyperlink ref="K41" r:id="rId315" tooltip="https://m.media-amazon.com/images/I/41C7wf1aFFL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId316" tooltip="https://www.amazon.co.jp/dp/B0HHM96S2L"/>
     <hyperlink ref="M41" r:id="rId317" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N41" r:id="rId318"/>
-    <hyperlink ref="AW41" r:id="rId319" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AW2A52M1BCKPL"/>
-    <hyperlink ref="C42" r:id="rId320" tooltip="https://www.amazon.co.jp/dp/B0HKYTFSJD"/>
-    <hyperlink ref="G42" r:id="rId321" tooltip="https://www.amazon.co.jp/TopDuterpick/b/ref=bl_dp_s_web_8448083051?ie=UTF8&amp;node=8448083051&amp;field-lbr_brands_browse-bin=TopDuterpick"/>
-    <hyperlink ref="J42" r:id="rId322" tooltip="https://www.amazon.co.jp/dp/B0HKYTFSJD?psc=1"/>
-    <hyperlink ref="K42" r:id="rId323" tooltip="https://m.media-amazon.com/images/I/41srV4Bdl3L._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId324" tooltip="https://www.amazon.co.jp/dp/B0HKYTFSJD"/>
-    <hyperlink ref="M42" r:id="rId325" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
-    <hyperlink ref="N42" r:id="rId326"/>
-    <hyperlink ref="AW42" r:id="rId327" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A18CF0AX3KZRVX"/>
-    <hyperlink ref="C43" r:id="rId328" tooltip="https://www.amazon.co.jp/dp/B08R3LF57P"/>
-    <hyperlink ref="G43" r:id="rId329" tooltip="https://www.amazon.co.jp/stores/KEEPOW/page/21523984-F72B-4ED5-8C28-45B0588E2513?lp_asin=B08R3LF57P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J43" r:id="rId330" tooltip="https://www.amazon.co.jp/dp/B08R3LF57P?psc=1"/>
-    <hyperlink ref="K43" r:id="rId331" tooltip="https://m.media-amazon.com/images/I/41AHQ4cHR8L._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId332" tooltip="https://www.amazon.co.jp/dp/B08R3LF57P"/>
-    <hyperlink ref="M43" r:id="rId333" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
-    <hyperlink ref="N43" r:id="rId334"/>
-    <hyperlink ref="AW43" r:id="rId335" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A30T80D6SCTMYZ"/>
-    <hyperlink ref="C44" r:id="rId336" tooltip="https://www.amazon.co.jp/dp/B0DRCGRJSR"/>
-    <hyperlink ref="G44" r:id="rId337" tooltip="https://www.amazon.co.jp/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0DRCGRJSR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J44" r:id="rId338" tooltip="https://www.amazon.co.jp/dp/B0DRCGRJSR?psc=1"/>
-    <hyperlink ref="K44" r:id="rId339" tooltip="https://m.media-amazon.com/images/I/41wLqF+bzbL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId340" tooltip="https://www.amazon.co.jp/dp/B0DRCGRJSR"/>
-    <hyperlink ref="M44" r:id="rId341" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
-    <hyperlink ref="N44" r:id="rId342"/>
-    <hyperlink ref="AW44" r:id="rId343" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES"/>
-    <hyperlink ref="C45" r:id="rId344" tooltip="https://www.amazon.co.jp/dp/B0HHM96S2L"/>
-    <hyperlink ref="G45" r:id="rId345" tooltip="https://www.amazon.co.jp/udodik/b/ref=bl_dp_s_web_21106953051?ie=UTF8&amp;node=21106953051&amp;field-lbr_brands_browse-bin=udodik"/>
-    <hyperlink ref="J45" r:id="rId346" tooltip="https://www.amazon.co.jp/dp/B0HHM96S2L?psc=1"/>
-    <hyperlink ref="K45" r:id="rId347" tooltip="https://m.media-amazon.com/images/I/41C7wf1aFFL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId348" tooltip="https://www.amazon.co.jp/dp/B0HHM96S2L"/>
-    <hyperlink ref="M45" r:id="rId349" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
-    <hyperlink ref="N45" r:id="rId350"/>
-    <hyperlink ref="AW45" r:id="rId351" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3LLGXOKFXGBZY"/>
-    <hyperlink ref="C46" r:id="rId352" tooltip="https://www.amazon.co.jp/dp/B0151FQ7PU"/>
-    <hyperlink ref="G46" r:id="rId353" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J46" r:id="rId354" tooltip="https://www.amazon.co.jp/dp/B0151FQ7PU?psc=1"/>
-    <hyperlink ref="K46" r:id="rId355" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61LMfetbCwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId356" tooltip="https://www.amazon.co.jp/dp/B0151FQ7PU"/>
-    <hyperlink ref="C47" r:id="rId357" tooltip="https://www.amazon.co.jp/dp/B09JJLTTX3"/>
-    <hyperlink ref="G47" r:id="rId358" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J47" r:id="rId359" tooltip="https://www.amazon.co.jp/dp/B09JJLTTX3?psc=1"/>
-    <hyperlink ref="K47" r:id="rId360" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41s1gdhaMXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId361" tooltip="https://www.amazon.co.jp/dp/B09JJLTTX3"/>
-    <hyperlink ref="C48" r:id="rId362" tooltip="https://www.amazon.co.jp/dp/B0CZ3TPQLS"/>
-    <hyperlink ref="G48" r:id="rId363" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J48" r:id="rId364" tooltip="https://www.amazon.co.jp/dp/B0CZ3TPQLS?psc=1"/>
-    <hyperlink ref="K48" r:id="rId365" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51f3q63b8bL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId366" tooltip="https://www.amazon.co.jp/dp/B0CZ3TPQLS"/>
-    <hyperlink ref="C49" r:id="rId367" tooltip="https://www.amazon.co.jp/dp/B0DC9P3BH4"/>
-    <hyperlink ref="G49" r:id="rId368" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J49" r:id="rId369" tooltip="https://www.amazon.co.jp/dp/B0DC9P3BH4?psc=1"/>
-    <hyperlink ref="K49" r:id="rId370" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71pzrJ+pdoL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId371" tooltip="https://www.amazon.co.jp/dp/B0DC9P3BH4"/>
-    <hyperlink ref="C50" r:id="rId372" tooltip="https://www.amazon.co.jp/dp/B0FL17N46W"/>
-    <hyperlink ref="G50" r:id="rId373" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J50" r:id="rId374" tooltip="https://www.amazon.co.jp/dp/B0FL17N46W?psc=1"/>
-    <hyperlink ref="K50" r:id="rId375" tooltip="https://images-fe.ssl-images-amazon.com/images/I/614fPWqO3uL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId376" tooltip="https://www.amazon.co.jp/dp/B0FL17N46W"/>
-    <hyperlink ref="C51" r:id="rId377" tooltip="https://www.amazon.co.jp/dp/B0FPWXHGQK"/>
-    <hyperlink ref="G51" r:id="rId378" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J51" r:id="rId379" tooltip="https://www.amazon.co.jp/dp/B0FPWXHGQK?psc=1"/>
-    <hyperlink ref="K51" r:id="rId380" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61ojBNldYaL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId381" tooltip="https://www.amazon.co.jp/dp/B0FPWXHGQK"/>
+    <hyperlink ref="AW41" r:id="rId319" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3LLGXOKFXGBZY"/>
+    <hyperlink ref="C42" r:id="rId320" tooltip="https://www.amazon.co.jp/dp/B0151FQ7PU"/>
+    <hyperlink ref="G42" r:id="rId321" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J42" r:id="rId322" tooltip="https://www.amazon.co.jp/dp/B0151FQ7PU?psc=1"/>
+    <hyperlink ref="K42" r:id="rId323" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61LMfetbCwL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId324" tooltip="https://www.amazon.co.jp/dp/B0151FQ7PU"/>
+    <hyperlink ref="C43" r:id="rId325" tooltip="https://www.amazon.co.jp/dp/B09JJLTTX3"/>
+    <hyperlink ref="G43" r:id="rId326" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J43" r:id="rId327" tooltip="https://www.amazon.co.jp/dp/B09JJLTTX3?psc=1"/>
+    <hyperlink ref="K43" r:id="rId328" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41s1gdhaMXL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId329" tooltip="https://www.amazon.co.jp/dp/B09JJLTTX3"/>
+    <hyperlink ref="C44" r:id="rId330" tooltip="https://www.amazon.co.jp/dp/B0CZ3TPQLS"/>
+    <hyperlink ref="G44" r:id="rId331" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J44" r:id="rId332" tooltip="https://www.amazon.co.jp/dp/B0CZ3TPQLS?psc=1"/>
+    <hyperlink ref="K44" r:id="rId333" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51f3q63b8bL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L44" r:id="rId334" tooltip="https://www.amazon.co.jp/dp/B0CZ3TPQLS"/>
+    <hyperlink ref="C45" r:id="rId335" tooltip="https://www.amazon.co.jp/dp/B0DC9P3BH4"/>
+    <hyperlink ref="G45" r:id="rId336" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J45" r:id="rId337" tooltip="https://www.amazon.co.jp/dp/B0DC9P3BH4?psc=1"/>
+    <hyperlink ref="K45" r:id="rId338" tooltip="https://images-fe.ssl-images-amazon.com/images/I/71pzrJ+pdoL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L45" r:id="rId339" tooltip="https://www.amazon.co.jp/dp/B0DC9P3BH4"/>
+    <hyperlink ref="C46" r:id="rId340" tooltip="https://www.amazon.co.jp/dp/B0FL17N46W"/>
+    <hyperlink ref="G46" r:id="rId341" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J46" r:id="rId342" tooltip="https://www.amazon.co.jp/dp/B0FL17N46W?psc=1"/>
+    <hyperlink ref="K46" r:id="rId343" tooltip="https://images-fe.ssl-images-amazon.com/images/I/614fPWqO3uL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L46" r:id="rId344" tooltip="https://www.amazon.co.jp/dp/B0FL17N46W"/>
+    <hyperlink ref="C47" r:id="rId345" tooltip="https://www.amazon.co.jp/dp/B0FPWXHGQK"/>
+    <hyperlink ref="G47" r:id="rId346" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J47" r:id="rId347" tooltip="https://www.amazon.co.jp/dp/B0FPWXHGQK?psc=1"/>
+    <hyperlink ref="K47" r:id="rId348" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61ojBNldYaL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId349" tooltip="https://www.amazon.co.jp/dp/B0FPWXHGQK"/>
   </hyperlinks>
-  <drawing r:id="rId382"/>
+  <drawing r:id="rId350"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -18257,7 +17189,7 @@
         <v>14510.010300044783</v>
       </c>
       <c r="G2" s="19">
-        <v>0.4377573024897079</v>
+        <v>0.44375993640699524</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18278,7 +17210,7 @@
         <v>12678.125281658406</v>
       </c>
       <c r="G3" s="19">
-        <v>0.21750637129974515</v>
+        <v>0.22048887122416533</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18299,7 +17231,7 @@
         <v>19510.19794344473</v>
       </c>
       <c r="G4" s="19">
-        <v>0.07625955694961772</v>
+        <v>0.07730524642289348</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18320,7 +17252,7 @@
         <v>19980.0</v>
       </c>
       <c r="G5" s="19">
-        <v>0.022250539109978436</v>
+        <v>0.02255564387917329</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18341,7 +17273,7 @@
         <v>29800.0</v>
       </c>
       <c r="G6" s="19">
-        <v>0.01284061948637522</v>
+        <v>0.013016693163751987</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18362,7 +17294,7 @@
         <v>28800.0</v>
       </c>
       <c r="G7" s="19">
-        <v>0.01264457949421682</v>
+        <v>0.012817965023847376</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18383,154 +17315,154 @@
         <v>8460.25</v>
       </c>
       <c r="G8" s="19">
-        <v>0.03136639874534405</v>
+        <v>0.03179650238473768</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>PLUS MINUS ZERO</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="B9" s="13">
-        <v>165</v>
+        <v>303</v>
       </c>
       <c r="C9" s="13">
-        <v>2668600</v>
+        <v>2489751</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13">
-        <v>16173.333333333334</v>
+        <v>8217.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.016173299353068025</v>
+        <v>0.03010731319554849</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>M Mistsince</t>
         </is>
       </c>
       <c r="B10" s="13">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="C10" s="13">
-        <v>2489751</v>
+        <v>2469405</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="13">
-        <v>8217.0</v>
+        <v>8485.927835051547</v>
       </c>
       <c r="G10" s="19">
-        <v>0.029700058811997648</v>
+        <v>0.028914944356120825</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>M Mistsince</t>
+          <t>KOJIHOMU</t>
         </is>
       </c>
       <c r="B11" s="13">
-        <v>291</v>
+        <v>160</v>
       </c>
       <c r="C11" s="13">
-        <v>2469405</v>
+        <v>2236800</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13">
-        <v>8485.927835051547</v>
+        <v>13980.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.028523818859047246</v>
+        <v>0.01589825119236884</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>KOJIHOMU</t>
+          <t>Amazonベーシック(Amazon Basics)</t>
         </is>
       </c>
       <c r="B12" s="13">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="C12" s="13">
-        <v>2236800</v>
+        <v>2003919</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13">
-        <v>13980.0</v>
+        <v>10383.0</v>
       </c>
       <c r="G12" s="19">
-        <v>0.015683199372672024</v>
+        <v>0.01917726550079491</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Amazonベーシック(Amazon Basics)</t>
+          <t>G-KiKi</t>
         </is>
       </c>
       <c r="B13" s="13">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="C13" s="13">
-        <v>2003919</v>
+        <v>1982166</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13">
-        <v>10383.0</v>
+        <v>19625.40594059406</v>
       </c>
       <c r="G13" s="19">
-        <v>0.01891785924328563</v>
+        <v>0.01003577106518283</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>G-KiKi</t>
+          <t>Hearten</t>
         </is>
       </c>
       <c r="B14" s="13">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="C14" s="13">
-        <v>1982166</v>
+        <v>1660849</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13">
-        <v>19625.40594059406</v>
+        <v>10999.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.009900019603999216</v>
+        <v>0.015003974562798093</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Hearten</t>
+          <t>PLUS MINUS ZERO</t>
         </is>
       </c>
       <c r="B15" s="13">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="C15" s="13">
-        <v>1660849</v>
+        <v>1647800</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
       <c r="F15" s="13">
-        <v>10999.0</v>
+        <v>15400.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.014801019407959224</v>
+        <v>0.010631955484896661</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18551,7 +17483,7 @@
         <v>12377.727272727272</v>
       </c>
       <c r="G16" s="19">
-        <v>0.008625759654969613</v>
+        <v>0.008744038155802861</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18572,7 +17504,7 @@
         <v>13741.51282051282</v>
       </c>
       <c r="G17" s="19">
-        <v>0.007645559694177613</v>
+        <v>0.007750397456279809</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18593,7 +17525,7 @@
         <v>16738.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.00607723975691041</v>
+        <v>0.006160572337042925</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18614,7 +17546,7 @@
         <v>17900.0</v>
       </c>
       <c r="G19" s="19">
-        <v>0.005489119780435208</v>
+        <v>0.005564387917329093</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18635,7 +17567,7 @@
         <v>14250.0</v>
       </c>
       <c r="G20" s="19">
-        <v>0.00597921976083121</v>
+        <v>0.00606120826709062</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18656,7 +17588,7 @@
         <v>9999.0</v>
       </c>
       <c r="G21" s="19">
-        <v>0.007547539698098412</v>
+        <v>0.007651033386327504</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18677,7 +17609,7 @@
         <v>23800.0</v>
       </c>
       <c r="G22" s="19">
-        <v>0.003136639874534405</v>
+        <v>0.003179650238473768</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18698,7 +17630,7 @@
         <v>12990.0</v>
       </c>
       <c r="G23" s="19">
-        <v>0.0016663399333464027</v>
+        <v>0.0016891891891891893</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18719,109 +17651,46 @@
         <v>14000.0</v>
       </c>
       <c r="G24" s="19">
-        <v>0.0009801999607920015</v>
+        <v>0.0009936406995230524</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>bumxca</t>
+          <t>TopDuterpick</t>
         </is>
       </c>
       <c r="B25" s="13">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C25" s="13">
-        <v>125378</v>
+        <v>116193</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13">
-        <v>5699.0</v>
+        <v>16599.0</v>
       </c>
       <c r="G25" s="19">
-        <v>0.0021564399137424034</v>
+        <v>0.0006955484896661367</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>TopDuterpick</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B26" s="13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C26" s="13">
-        <v>116193</v>
+        <v>0</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
-      <c r="F26" s="13">
-        <v>16599.0</v>
-      </c>
+      <c r="F26" s="13"/>
       <c r="G26" s="19">
-        <v>0.000686139972554401</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>KEEPOW</t>
-        </is>
-      </c>
-      <c r="B27" s="13">
-        <v>42</v>
-      </c>
-      <c r="C27" s="13">
-        <v>96558</v>
-      </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13">
-        <v>2299.0</v>
-      </c>
-      <c r="G27" s="19">
-        <v>0.004116839835326407</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>HAUSHOF</t>
-        </is>
-      </c>
-      <c r="B28" s="13">
-        <v>16</v>
-      </c>
-      <c r="C28" s="13">
-        <v>95680</v>
-      </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13">
-        <v>5980.0</v>
-      </c>
-      <c r="G28" s="19">
-        <v>0.0015683199372672025</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B29" s="13">
-        <v>0</v>
-      </c>
-      <c r="C29" s="13">
-        <v>0</v>
-      </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -18833,7 +17702,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -18897,7 +17766,7 @@
         <v>14510.010300044783</v>
       </c>
       <c r="G2" s="19">
-        <v>0.4377573024897079</v>
+        <v>0.44375993640699524</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18918,7 +17787,7 @@
         <v>13800.0</v>
       </c>
       <c r="G3" s="19">
-        <v>0.13781611448735542</v>
+        <v>0.13970588235294118</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18939,7 +17808,7 @@
         <v>19510.19794344473</v>
       </c>
       <c r="G4" s="19">
-        <v>0.07625955694961772</v>
+        <v>0.07730524642289348</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18960,7 +17829,7 @@
         <v>19980.0</v>
       </c>
       <c r="G5" s="19">
-        <v>0.022250539109978436</v>
+        <v>0.02255564387917329</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18981,7 +17850,7 @@
         <v>29800.0</v>
       </c>
       <c r="G6" s="19">
-        <v>0.01284061948637522</v>
+        <v>0.013016693163751987</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19002,7 +17871,7 @@
         <v>28800.0</v>
       </c>
       <c r="G7" s="19">
-        <v>0.01264457949421682</v>
+        <v>0.012817965023847376</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19023,7 +17892,7 @@
         <v>12000.0</v>
       </c>
       <c r="G8" s="19">
-        <v>0.028719858851205645</v>
+        <v>0.029113672496025436</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19044,7 +17913,7 @@
         <v>8905.051546391753</v>
       </c>
       <c r="G9" s="19">
-        <v>0.03803175847872966</v>
+        <v>0.038553259141494434</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19065,154 +17934,154 @@
         <v>8460.25</v>
       </c>
       <c r="G10" s="19">
-        <v>0.03136639874534405</v>
+        <v>0.03179650238473768</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>プラスマイナスゼロ</t>
+          <t>D shopone</t>
         </is>
       </c>
       <c r="B11" s="13">
-        <v>165</v>
+        <v>303</v>
       </c>
       <c r="C11" s="13">
-        <v>2668600</v>
+        <v>2489751</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13">
-        <v>16173.333333333334</v>
+        <v>8217.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.016173299353068025</v>
+        <v>0.03010731319554849</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>D shopone</t>
+          <t>Mistsince</t>
         </is>
       </c>
       <c r="B12" s="13">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="C12" s="13">
-        <v>2489751</v>
+        <v>2469405</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13">
-        <v>8217.0</v>
+        <v>8485.927835051547</v>
       </c>
       <c r="G12" s="19">
-        <v>0.029700058811997648</v>
+        <v>0.028914944356120825</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Mistsince</t>
+          <t>KOJIHOMU メーカー XCJ</t>
         </is>
       </c>
       <c r="B13" s="13">
-        <v>291</v>
+        <v>160</v>
       </c>
       <c r="C13" s="13">
-        <v>2469405</v>
+        <v>2236800</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13">
-        <v>8485.927835051547</v>
+        <v>13980.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.028523818859047246</v>
+        <v>0.01589825119236884</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>KOJIHOMU メーカー XCJ</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B14" s="13">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="C14" s="13">
-        <v>2236800</v>
+        <v>2003919</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13">
-        <v>13980.0</v>
+        <v>10383.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.015683199372672024</v>
+        <v>0.01917726550079491</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>GKK公式直営・安心保証</t>
         </is>
       </c>
       <c r="B15" s="13">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="C15" s="13">
-        <v>2003919</v>
+        <v>1982166</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
       <c r="F15" s="13">
-        <v>10383.0</v>
+        <v>19625.40594059406</v>
       </c>
       <c r="G15" s="19">
-        <v>0.01891785924328563</v>
+        <v>0.01003577106518283</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>GKK公式直営・安心保証</t>
+          <t>harmonyihome</t>
         </is>
       </c>
       <c r="B16" s="13">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="C16" s="13">
-        <v>1982166</v>
+        <v>1660849</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13">
-        <v>19625.40594059406</v>
+        <v>10999.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.009900019603999216</v>
+        <v>0.015003974562798093</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>harmonyihome</t>
+          <t>プラスマイナスゼロ</t>
         </is>
       </c>
       <c r="B17" s="13">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="C17" s="13">
-        <v>1660849</v>
+        <v>1647800</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
       <c r="F17" s="13">
-        <v>10999.0</v>
+        <v>15400.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.014801019407959224</v>
+        <v>0.010631955484896661</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19233,7 +18102,7 @@
         <v>13741.51282051282</v>
       </c>
       <c r="G18" s="19">
-        <v>0.007645559694177613</v>
+        <v>0.007750397456279809</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19254,7 +18123,7 @@
         <v>16738.0</v>
       </c>
       <c r="G19" s="19">
-        <v>0.00607723975691041</v>
+        <v>0.006160572337042925</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19275,7 +18144,7 @@
         <v>17900.0</v>
       </c>
       <c r="G20" s="19">
-        <v>0.005489119780435208</v>
+        <v>0.005564387917329093</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19296,7 +18165,7 @@
         <v>12200.0</v>
       </c>
       <c r="G21" s="19">
-        <v>0.007743579690256812</v>
+        <v>0.007849761526232114</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19317,7 +18186,7 @@
         <v>14250.0</v>
       </c>
       <c r="G22" s="19">
-        <v>0.00597921976083121</v>
+        <v>0.00606120826709062</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19338,7 +18207,7 @@
         <v>18816.0</v>
       </c>
       <c r="G23" s="19">
-        <v>0.004410899823564007</v>
+        <v>0.004471383147853736</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19359,7 +18228,7 @@
         <v>15000.0</v>
       </c>
       <c r="G24" s="19">
-        <v>0.005195059792197608</v>
+        <v>0.005266295707472178</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19380,7 +18249,7 @@
         <v>9999.0</v>
       </c>
       <c r="G25" s="19">
-        <v>0.007547539698098412</v>
+        <v>0.007651033386327504</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19401,7 +18270,7 @@
         <v>23800.0</v>
       </c>
       <c r="G26" s="19">
-        <v>0.003136639874534405</v>
+        <v>0.003179650238473768</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19422,7 +18291,7 @@
         <v>5640.0</v>
       </c>
       <c r="G27" s="19">
-        <v>0.004214859831405607</v>
+        <v>0.004272655007949126</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19443,7 +18312,7 @@
         <v>12990.0</v>
       </c>
       <c r="G28" s="19">
-        <v>0.0016663399333464027</v>
+        <v>0.0016891891891891893</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19464,109 +18333,46 @@
         <v>14000.0</v>
       </c>
       <c r="G29" s="19">
-        <v>0.0009801999607920015</v>
+        <v>0.0009936406995230524</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>bumxca（バムスカ）直営公式店</t>
+          <t>Duter</t>
         </is>
       </c>
       <c r="B30" s="13">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C30" s="13">
-        <v>125378</v>
+        <v>116193</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
       <c r="F30" s="13">
-        <v>5699.0</v>
+        <v>16599.0</v>
       </c>
       <c r="G30" s="19">
-        <v>0.0021564399137424034</v>
+        <v>0.0006955484896661367</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Duter</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B31" s="13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C31" s="13">
-        <v>116193</v>
+        <v>0</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
-      <c r="F31" s="13">
-        <v>16599.0</v>
-      </c>
+      <c r="F31" s="13"/>
       <c r="G31" s="19">
-        <v>0.000686139972554401</v>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Roberts Robot</t>
-        </is>
-      </c>
-      <c r="B32" s="13">
-        <v>42</v>
-      </c>
-      <c r="C32" s="13">
-        <v>96558</v>
-      </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13">
-        <v>2299.0</v>
-      </c>
-      <c r="G32" s="19">
-        <v>0.004116839835326407</v>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>Megastar Store</t>
-        </is>
-      </c>
-      <c r="B33" s="13">
-        <v>16</v>
-      </c>
-      <c r="C33" s="13">
-        <v>95680</v>
-      </c>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13">
-        <v>5980.0</v>
-      </c>
-      <c r="G33" s="19">
-        <v>0.0015683199372672025</v>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B34" s="13">
-        <v>0</v>
-      </c>
-      <c r="C34" s="13">
-        <v>0</v>
-      </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="19">
         <v>0.0</v>
       </c>
     </row>
